--- a/wrong_words.xlsx
+++ b/wrong_words.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:E164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,11 @@
           <t>时间</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>错误次数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -457,6 +462,9 @@
       <c r="D2" s="1" t="n">
         <v>46080.46063228009</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -473,6 +481,9 @@
       <c r="D3" s="1" t="n">
         <v>46080.46183247685</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -489,6 +500,9 @@
       <c r="D4" s="1" t="n">
         <v>46080.46213064815</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -505,6 +519,9 @@
       <c r="D5" s="1" t="n">
         <v>46080.46235232639</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -521,6 +538,9 @@
       <c r="D6" s="1" t="n">
         <v>46080.46235446759</v>
       </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -537,6 +557,9 @@
       <c r="D7" s="1" t="n">
         <v>46080.46263118056</v>
       </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -553,6 +576,9 @@
       <c r="D8" s="1" t="n">
         <v>46080.46348469907</v>
       </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -569,6 +595,9 @@
       <c r="D9" s="1" t="n">
         <v>46080.46427136574</v>
       </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -585,6 +614,9 @@
       <c r="D10" s="1" t="n">
         <v>46080.46472703704</v>
       </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -601,6 +633,9 @@
       <c r="D11" s="1" t="n">
         <v>46080.46550108797</v>
       </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -617,6 +652,9 @@
       <c r="D12" s="1" t="n">
         <v>46080.4666321412</v>
       </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -633,6 +671,9 @@
       <c r="D13" s="1" t="n">
         <v>46080.46663798611</v>
       </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -649,6 +690,9 @@
       <c r="D14" s="1" t="n">
         <v>46080.46663825231</v>
       </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -665,6 +709,9 @@
       <c r="D15" s="1" t="n">
         <v>46080.46663879629</v>
       </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -681,6 +728,9 @@
       <c r="D16" s="1" t="n">
         <v>46080.4666390162</v>
       </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -697,6 +747,9 @@
       <c r="D17" s="1" t="n">
         <v>46080.46664003472</v>
       </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -713,6 +766,9 @@
       <c r="D18" s="1" t="n">
         <v>46080.4666419213</v>
       </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -729,6 +785,9 @@
       <c r="D19" s="1" t="n">
         <v>46080.4666434375</v>
       </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -745,6 +804,9 @@
       <c r="D20" s="1" t="n">
         <v>46080.46664473379</v>
       </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -761,6 +823,9 @@
       <c r="D21" s="1" t="n">
         <v>46080.46664630787</v>
       </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -777,6 +842,9 @@
       <c r="D22" s="1" t="n">
         <v>46080.46664767361</v>
       </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -793,6 +861,9 @@
       <c r="D23" s="1" t="n">
         <v>46080.46664902778</v>
       </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -809,6 +880,9 @@
       <c r="D24" s="1" t="n">
         <v>46080.46665060185</v>
       </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -825,6 +899,9 @@
       <c r="D25" s="1" t="n">
         <v>46080.46665228009</v>
       </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -841,6 +918,9 @@
       <c r="D26" s="1" t="n">
         <v>46080.46665380787</v>
       </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -857,6 +937,9 @@
       <c r="D27" s="1" t="n">
         <v>46080.46665553241</v>
       </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -873,6 +956,9 @@
       <c r="D28" s="1" t="n">
         <v>46080.46665704861</v>
       </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -889,6 +975,9 @@
       <c r="D29" s="1" t="n">
         <v>46080.46665885417</v>
       </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -905,6 +994,9 @@
       <c r="D30" s="1" t="n">
         <v>46080.46666043982</v>
       </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -919,7 +1011,10 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" s="1" t="n">
-        <v>46080.4666640162</v>
+        <v>46080.67821839121</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -935,7 +1030,10 @@
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" s="1" t="n">
-        <v>46080.46666576389</v>
+        <v>46080.69804697917</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -953,6 +1051,9 @@
       <c r="D33" s="1" t="n">
         <v>46080.46666758101</v>
       </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -969,6 +1070,9 @@
       <c r="D34" s="1" t="n">
         <v>46080.466669375</v>
       </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -985,6 +1089,9 @@
       <c r="D35" s="1" t="n">
         <v>46080.46667130787</v>
       </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1001,6 +1108,9 @@
       <c r="D36" s="1" t="n">
         <v>46080.46667318287</v>
       </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1017,6 +1127,9 @@
       <c r="D37" s="1" t="n">
         <v>46080.46667506945</v>
       </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1031,7 +1144,10 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" s="1" t="n">
-        <v>46080.4666771412</v>
+        <v>46080.68047622685</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1049,6 +1165,9 @@
       <c r="D39" s="1" t="n">
         <v>46080.46667913195</v>
       </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1065,6 +1184,9 @@
       <c r="D40" s="1" t="n">
         <v>46080.46668106481</v>
       </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1081,6 +1203,9 @@
       <c r="D41" s="1" t="n">
         <v>46080.46668291667</v>
       </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1097,6 +1222,9 @@
       <c r="D42" s="1" t="n">
         <v>46080.46668493056</v>
       </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1113,6 +1241,9 @@
       <c r="D43" s="1" t="n">
         <v>46080.46668684028</v>
       </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1129,6 +1260,9 @@
       <c r="D44" s="1" t="n">
         <v>46080.46668894676</v>
       </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1145,6 +1279,9 @@
       <c r="D45" s="1" t="n">
         <v>46080.46669075231</v>
       </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1161,6 +1298,9 @@
       <c r="D46" s="1" t="n">
         <v>46080.46669271991</v>
       </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1177,6 +1317,9 @@
       <c r="D47" s="1" t="n">
         <v>46080.46669469908</v>
       </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1193,6 +1336,9 @@
       <c r="D48" s="1" t="n">
         <v>46080.4666965625</v>
       </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1209,6 +1355,9 @@
       <c r="D49" s="1" t="n">
         <v>46080.46669842592</v>
       </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1225,6 +1374,9 @@
       <c r="D50" s="1" t="n">
         <v>46080.46670033565</v>
       </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1241,6 +1393,9 @@
       <c r="D51" s="1" t="n">
         <v>46080.4667022338</v>
       </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1257,6 +1412,9 @@
       <c r="D52" s="1" t="n">
         <v>46080.4667040162</v>
       </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1271,7 +1429,10 @@
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" s="1" t="n">
-        <v>46080.46670597222</v>
+        <v>46080.6951031713</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1289,6 +1450,9 @@
       <c r="D54" s="1" t="n">
         <v>46080.46670770834</v>
       </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1305,6 +1469,9 @@
       <c r="D55" s="1" t="n">
         <v>46080.46670940972</v>
       </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1321,6 +1488,9 @@
       <c r="D56" s="1" t="n">
         <v>46080.46671119213</v>
       </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1337,6 +1507,9 @@
       <c r="D57" s="1" t="n">
         <v>46080.46671306713</v>
       </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1353,6 +1526,9 @@
       <c r="D58" s="1" t="n">
         <v>46080.46671515046</v>
       </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1369,6 +1545,9 @@
       <c r="D59" s="1" t="n">
         <v>46080.46671709491</v>
       </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1385,6 +1564,9 @@
       <c r="D60" s="1" t="n">
         <v>46080.46671886574</v>
       </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1401,6 +1583,9 @@
       <c r="D61" s="1" t="n">
         <v>46080.46672407407</v>
       </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1419,7 +1604,2340 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46080.47503664322</v>
+        <v>46080.47503664352</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>経済（けいざい）</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>经济</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>→ 日本経済の現状を分析する。</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>46080.60748118055</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>目的（もくてき）</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>→ 訪問の目的は何ですか。</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>46080.56176550926</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>伝統（でんとう）</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>传统</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>→ 伝統を大切にする。</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>46080.56200450232</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>産業（さんぎょう）</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>→ 観光産業が発展している。</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>46080.56254891204</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>地域（ちいき）</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>→ この地域は静かだ。</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>46080.56325935185</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>情報（じょうほう）</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>→ 正確な情報を集める。</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>46080.56342862269</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>政府（せいふ）</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>政府</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>→ 政府は新しい政策を発表した。</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>46080.5639512037</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>評価（ひょうか）</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>评价</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>→ 努力が高く評価された。</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>46080.56455998842</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>期間（きかん）</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>期间</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>→ 申込期間は今月末までだ。</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>46080.56505081018</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>証拠（しょうこ）</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>→ 証拠が見つからない。</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>46080.56526182871</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>義務（ぎむ）</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>义务</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>→ 納税は国民の義務である。</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>46080.56577579861</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>都市（とし）</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>→ 大都市で生活している。</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>46080.60696920139</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>地方（ちほう）</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>地方</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>→ 地方の文化を紹介する。</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>46080.56619986111</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>責任（せきにん）</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>责任</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>→ 彼はその責任を負うべきだ。</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>46080.56655037037</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>人口（じんこう）</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>人口</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>→ 人口が減少している。</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>46080.56695744213</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>対策（たいさく）</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>对策</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>→ 地震対策が必要だ。</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>46080.56788527778</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>課題（かだい）</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>课题</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>→ 環境問題は大きな課題だ。</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>46080.56806637732</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>法律（ほうりつ）</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>法律</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>→ 法律を守らなければならない。</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>46080.6086725463</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>判断（はんだん）</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>判断</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>→ 正しい判断をすることが大切だ。</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>46080.56845658565</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>時期（じき）</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>时期</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>→ 今は旅行に最適な時期だ。</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>46080.56894141204</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>傾向（けいこう）</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>倾向</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>→ 最近、在宅勤務が増える傾向にある。</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>46080.56906857639</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>意識（いしき）</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>意识</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>→ 健康への意識が高まっている。</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>46080.56927060185</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>技術（ぎじゅつ）</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>技术</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>→ 新しい技術が開発された。</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>46080.56958121528</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>政策（せいさく）</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>政策</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>→ 政策の効果を検討する。</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>46080.57033020833</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>義務（ぎむ）</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>义务</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>→ 納税は国民の義務である。</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>46080.57131366898</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>判断（はんだん）</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>判断</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>→ 正しい判断をすることが大切だ。</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>46080.57155042824</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>事実（じじつ）</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>事实</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>→ それは事実ですか。</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>46080.5719875463</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>証拠（しょうこ）</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>→ 証拠が見つからない。</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>46080.57285732639</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>対策（たいさく）</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>对策</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>→ 地震対策が必要だ。</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>46080.57404704861</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>成果（せいか）</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>成果</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>→ 研究の成果が発表された。</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>46080.57461549769</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>地方（ちほう）</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>地方</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>→ 地方の文化を紹介する。</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>46080.57541208333</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>情報（じょうほう）</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>→ 正確な情報を集める。</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>46080.57556856482</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>経済（けいざい）</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>经济</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>→ 日本経済の現状を分析する。</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>46080.57623722222</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>責任（せきにん）</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>责任</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>→ 彼はその責任を負うべきだ。</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>46080.5766812037</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>産業（さんぎょう）</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>→ 観光産業が発展している。</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>46080.57832047454</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>制限（せいげん）</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>限制</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>→ 人数に制限がある。</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>46080.57880002315</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>地域（ちいき）</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>→ この地域は静かだ。</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="n">
+        <v>46080.5793759375</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>技術（ぎじゅつ）</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>技术</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>→ 新しい技術が開発された。</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="n">
+        <v>46080.58013798611</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>伝統（でんとう）</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>传统</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>→ 伝統を大切にする。</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>46080.58084075231</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>法律（ほうりつ）</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>法律</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>→ 法律を守らなければならない。</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>46080.58260957176</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>都市（とし）</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>→ 大都市で生活している。</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>46080.58285303241</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>傾向（けいこう）</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>倾向</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>→ 最近、在宅勤務が増える傾向にある。</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>46080.58348328704</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>収入（しゅうにゅう）</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>→ 収入が増えれば生活も楽になる。</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>46080.5926562963</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>支出（ししゅつ）</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>→ 今月は支出が多かった。</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="n">
+        <v>46080.59306905093</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>価値（かち）</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>价值</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>→ この経験には大きな価値がある。</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>46080.59345513889</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>利益（りえき）</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>利益</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>→ 会社は大きな利益を上げた。</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="n">
+        <v>46080.59370576389</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>損失（そんしつ）</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>损失</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>→ 事故による損失は大きい。</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="n">
+        <v>46080.59397033565</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>契約（けいやく）</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>合同</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>→ 来週、契約を結ぶ予定だ。</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="n">
+        <v>46080.59444777778</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>法律（ほうりつ）</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>法律</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>→ 法律を守らなければならない。</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="n">
+        <v>46080.59664722222</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>判断（はんだん）</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>判断</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>→ 正しい判断をすることが大切だ。</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="n">
+        <v>46080.59795071759</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>産業（さんぎょう）</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>→ 観光産業が発展している。</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="n">
+        <v>46080.59834469907</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>責任（せきにん）</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>责任</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>→ 彼はその責任を負うべきだ。</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="n">
+        <v>46080.59851604167</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>都市（とし）</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>→ 大都市で生活している。</t>
+        </is>
+      </c>
+      <c r="D115" s="1" t="n">
+        <v>46080.59874068287</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>経済（けいざい）</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>经济</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>→ 日本経済の現状を分析する。</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="n">
+        <v>46080.5989090625</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>証拠（しょうこ）</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>→ 証拠が見つからない。</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="n">
+        <v>46080.59910177084</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>傾向（けいこう）</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>倾向</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>→ 最近、在宅勤務が増える傾向にある。</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>46080.5991597338</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>技術（ぎじゅつ）</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>技术</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>→ 新しい技術が開発された。</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>46080.59980128472</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>情報（じょうほう）</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>信息</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>→ 正確な情報を集める。</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>46080.59990939814</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>地域（ちいき）</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>→ この地域は静かだ。</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>46080.60004016204</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>確かめる（たしかめる）</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>确认</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>→ 答えを確かめる。</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>46080.69146634259</v>
+      </c>
+      <c r="E122" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>たくさん</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>很多</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>→ 本をたくさん読む。</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>46080.61240799769</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>返る（かえる）</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>归还（自动）</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>→ 手紙が返ってきた。</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>46080.67669332176</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>回復（かいふく）</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>恢复</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>→ 体力が回復した。</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>46080.61294725694</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>被災者（ひさいしゃ）</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>受灾者</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>→ 被災者を支援する。</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>46080.70016293981</v>
+      </c>
+      <c r="E126" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>市場（しじょう）</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>市场</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>→ 市場を拡大する。</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>46080.67841640046</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>温かい（あたたかい）</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>温暖的（物体/天气）</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>→ 温かいスープ。</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>46080.67897109954</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>逃げる（にげる）</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>逃跑</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>→ 危険から逃げる。</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>46080.61389380787</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>面倒な（めんどうな）</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>麻烦（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" s="1" t="n">
+        <v>46080.67461975694</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>提供（ていきょう）</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>提供</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>→ 情報を提供する。</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>46080.61430228009</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>また</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>又/而且</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>→ 彼は優しい。また、頭も良い。</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>46080.61438069445</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>調査（ちょうさ）</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>调查</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>→ 市場調査を行う。</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>46080.61464663195</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>悲しむ（かなしむ）</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>悲伤</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>→ ニュースを聞いて悲しむ。</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>46080.67708070602</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>一度（いちど）</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>一次</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>→ 一度行ってみる。</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>46080.61502732639</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>折る（おる）</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>折（他动）</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>→ 紙を折る。</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>46080.61510775463</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>異常（いじょう）</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>异常的</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>→ 異常な天気。</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>46080.6804209375</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>寄付（きふ）</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>捐款</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>→ 被災地に寄付する。</t>
+        </is>
+      </c>
+      <c r="D138" s="1" t="n">
+        <v>46080.70094480948</v>
+      </c>
+      <c r="E138" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>感謝する（かんしゃする）</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>感谢</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>→ 助けてくれて感謝する。</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="n">
+        <v>46080.61549799769</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>就職（しゅうしょく）</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>就业</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>→ 大学卒業後、就職した。</t>
+        </is>
+      </c>
+      <c r="D140" s="1" t="n">
+        <v>46080.67273118056</v>
+      </c>
+      <c r="E140" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>平和（へいわ）</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>和平</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>→ 世界平和を願う。</t>
+        </is>
+      </c>
+      <c r="D141" s="1" t="n">
+        <v>46080.6159328588</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>具体例（ぐたいれい）</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>具体例</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>→ 具体例を示してください。</t>
+        </is>
+      </c>
+      <c r="D142" s="1" t="n">
+        <v>46080.67368262731</v>
+      </c>
+      <c r="E142" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>なお</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>此外/而且</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>→ 注意してください。なお、禁止事項も守ってください。</t>
+        </is>
+      </c>
+      <c r="D143" s="1" t="n">
+        <v>46080.61597976852</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>中断（ちゅうだん）</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>中断</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>→ 作業を中断する。</t>
+        </is>
+      </c>
+      <c r="D144" s="1" t="n">
+        <v>46080.61601502315</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>けれど</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>虽然/但是</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>→ 雨だ、けれど行く。</t>
+        </is>
+      </c>
+      <c r="D145" s="1" t="n">
+        <v>46080.70040850694</v>
+      </c>
+      <c r="E145" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>実施する（じっしする）</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>实施</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>→ 新しい制度を実施する。</t>
+        </is>
+      </c>
+      <c r="D146" s="1" t="n">
+        <v>46080.61656789352</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>深い（ふかい）</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>深的</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>→ 深い池。</t>
+        </is>
+      </c>
+      <c r="D147" s="1" t="n">
+        <v>46080.6780844213</v>
+      </c>
+      <c r="E147" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>報道（ほうどう）</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>报道</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>→ 事件が報道された。</t>
+        </is>
+      </c>
+      <c r="D148" s="1" t="n">
+        <v>46080.6167668287</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>なるべく</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>尽量</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>→ なるべく早く来てください。</t>
+        </is>
+      </c>
+      <c r="D149" s="1" t="n">
+        <v>46080.68596370371</v>
+      </c>
+      <c r="E149" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>溶かす（とかす）</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>融化（他动）</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>→ バターを溶かす。</t>
+        </is>
+      </c>
+      <c r="D150" s="1" t="n">
+        <v>46080.69160017361</v>
+      </c>
+      <c r="E150" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>比較する（ひかくする）</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>比较</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>→ 二つのデータを比較する。</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="n">
+        <v>46080.68646912037</v>
+      </c>
+      <c r="E151" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>育てる（そだてる）</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>培养</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>→ 子供を育てる。</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="n">
+        <v>46080.67791672454</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>激しい（はげしい）</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>激烈的</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>→ 激しい運動。</t>
+        </is>
+      </c>
+      <c r="D153" s="1" t="n">
+        <v>46080.69443997685</v>
+      </c>
+      <c r="E153" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>嫌いな（きらいな）</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>讨厌（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" s="1" t="n">
+        <v>46080.69405138889</v>
+      </c>
+      <c r="E154" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>不平等（ふびょうどう）</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>不平等（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" s="1" t="n">
+        <v>46080.69169520833</v>
+      </c>
+      <c r="E155" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>許可証（きょかしょう）</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>许可证</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>→ 許可証を提示する。</t>
+        </is>
+      </c>
+      <c r="D156" s="1" t="n">
+        <v>46080.61754525463</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>少々（しょうしょう）</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>稍微（更书面）</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>→ 少々お待ちください。</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>46080.6772082176</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ちゃんと</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>好好地</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>→ ちゃんと答える。</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>46080.67439758102</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>出席（しゅっせき）</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>出席</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>→ 授業に出席する。</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>46080.68578065973</v>
+      </c>
+      <c r="E159" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>割る（わる）</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>打碎（他动）</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>→ ガラスを割る。</t>
+        </is>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>46080.61780950231</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>明るい（あかるい）</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>明亮/开朗</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>→ 明るい笑顔。</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="n">
+        <v>46080.61791552083</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>折る（おる）</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>折</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>→ 紙を折る。</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="n">
+        <v>46080.67626359954</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>割る（わる）</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>打碎</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>→ コップを割る。</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="n">
+        <v>46080.68632105324</v>
+      </c>
+      <c r="E163" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>平和（へいわ）</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>和平的（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" s="1" t="n">
+        <v>46080.69992422454</v>
+      </c>
+      <c r="E164" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/wrong_words.xlsx
+++ b/wrong_words.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E164"/>
+  <dimension ref="A1:E339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="1" t="n">
-        <v>46080.46183247685</v>
+        <v>46083.6439582176</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -517,10 +517,10 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="1" t="n">
-        <v>46080.46235232639</v>
+        <v>46083.64062782408</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -574,10 +574,10 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" s="1" t="n">
-        <v>46080.46348469907</v>
+        <v>46083.45918741898</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -669,10 +669,10 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" s="1" t="n">
-        <v>46080.46663798611</v>
+        <v>46083.47617060185</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -821,10 +821,10 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" s="1" t="n">
-        <v>46080.46664630787</v>
+        <v>46081.57325398148</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -878,10 +878,10 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" s="1" t="n">
-        <v>46080.46665060185</v>
+        <v>46083.47587528935</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -897,10 +897,10 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" s="1" t="n">
-        <v>46080.46665228009</v>
+        <v>46083.58243572916</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1163,10 +1163,10 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" s="1" t="n">
-        <v>46080.46667913195</v>
+        <v>46083.45678017361</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -1239,10 +1239,10 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" s="1" t="n">
-        <v>46080.46668684028</v>
+        <v>46083.45132778935</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1315,10 +1315,10 @@
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" s="1" t="n">
-        <v>46080.46669469908</v>
+        <v>46083.59788269676</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1391,10 +1391,10 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" s="1" t="n">
-        <v>46080.4667022338</v>
+        <v>46083.45303177083</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -1543,10 +1543,10 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" s="1" t="n">
-        <v>46080.46671709491</v>
+        <v>46083.62219804398</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46080.56200450232</v>
+        <v>46081.40699491898</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46080.56619986111</v>
+        <v>46083.42941619213</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46080.56655037037</v>
+        <v>46081.40812126157</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46080.56906857639</v>
+        <v>46083.43582849537</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46080.59306905093</v>
+        <v>46083.4966546875</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46080.59370576389</v>
+        <v>46083.64152172454</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46080.70016293981</v>
+        <v>46081.40270194445</v>
       </c>
       <c r="E126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46080.61438069445</v>
+        <v>46083.43385356481</v>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46080.67708070602</v>
+        <v>46081.37734001158</v>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46080.70094480948</v>
+        <v>46080.70094481482</v>
       </c>
       <c r="E138" t="n">
         <v>5</v>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46080.61601502315</v>
+        <v>46081.43200761574</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46080.61656789352</v>
+        <v>46083.43744209491</v>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46080.6780844213</v>
+        <v>46083.48602541666</v>
       </c>
       <c r="E147" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46080.68596370371</v>
+        <v>46083.45729969908</v>
       </c>
       <c r="E149" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150">
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46080.69160017361</v>
+        <v>46081.37748003472</v>
       </c>
       <c r="E150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151">
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46080.69443997685</v>
+        <v>46083.4738440625</v>
       </c>
       <c r="E153" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154">
@@ -3712,10 +3712,10 @@
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" s="1" t="n">
-        <v>46080.69405138889</v>
+        <v>46083.40216436343</v>
       </c>
       <c r="E154" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155">
@@ -3731,10 +3731,10 @@
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" s="1" t="n">
-        <v>46080.69169520833</v>
+        <v>46083.43150489583</v>
       </c>
       <c r="E155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
@@ -3754,10 +3754,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46080.61754525463</v>
+        <v>46081.42599478009</v>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -3938,6 +3938,3983 @@
       </c>
       <c r="E164" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>明るい（あかるい）</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>明亮</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>→ 明るい部屋。</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="n">
+        <v>46083.4284556713</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>戻る（もどる）</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>返回</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>→ 家に戻る。</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="n">
+        <v>46081.4386966088</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>すこしも（少しも）</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>一点也不</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>→ 少しも怖くない。</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="n">
+        <v>46083.45695443287</v>
+      </c>
+      <c r="E167" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>とても</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>非常</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>→ とても美味しい。</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="n">
+        <v>46083.44990563657</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ぜんぜん（全然）</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>一点也不</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>→ 全然分からない。</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="n">
+        <v>46081.5699000926</v>
+      </c>
+      <c r="E169" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>整理する（せいりする）</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>整理</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>→ 書類を整理する。</t>
+        </is>
+      </c>
+      <c r="D170" s="1" t="n">
+        <v>46081.49424097222</v>
+      </c>
+      <c r="E170" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>便利な（べんりな）</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>方便（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" s="1" t="n">
+        <v>46083.43668841435</v>
+      </c>
+      <c r="E171" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>とりあえず</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>暂且/先</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>→ とりあえず座ってください。</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="n">
+        <v>46083.4581275</v>
+      </c>
+      <c r="E172" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>さきほど</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>刚才（书面）</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>→ さきほど電話がありました。</t>
+        </is>
+      </c>
+      <c r="D173" s="1" t="n">
+        <v>46083.44687914352</v>
+      </c>
+      <c r="E173" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>医療（いりょう）</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>→ 医療制度を改善する。</t>
+        </is>
+      </c>
+      <c r="D174" s="1" t="n">
+        <v>46081.44302641204</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>どうしても</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>无论如何</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>→ どうしても成功したい。</t>
+        </is>
+      </c>
+      <c r="D175" s="1" t="n">
+        <v>46083.45436300926</v>
+      </c>
+      <c r="E175" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>注意（ちゅうい）</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>→ 足元に注意してください。</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="n">
+        <v>46083.451595625</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>広い（ひろい）</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>宽广</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>→ 広い公園。</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="n">
+        <v>46081.44367083333</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>好調（こうちょう）</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>顺利的（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" s="1" t="n">
+        <v>46083.43229525463</v>
+      </c>
+      <c r="E178" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>苦しむ（くるしむ）</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>痛苦</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>→ 病気で苦しむ。</t>
+        </is>
+      </c>
+      <c r="D179" s="1" t="n">
+        <v>46081.55797784722</v>
+      </c>
+      <c r="E179" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>技術者（ぎじゅつしゃ）</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>技术人员</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>→ 優秀な技術者が必要だ。</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="n">
+        <v>46081.44446501158</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>修理する（しゅうりする）</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>修理</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>→ 車を修理する。</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="n">
+        <v>46081.48000659722</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>保険（ほけん）</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>保险</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>→ 保険に加入する。</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="n">
+        <v>46083.43726826389</v>
+      </c>
+      <c r="E182" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>警告（けいこく）</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>警告</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>→ 医者は彼に警告した。</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="n">
+        <v>46081.44512474537</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>過去（かこ）</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>过去</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>→ 過去を振り返る。</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="n">
+        <v>46081.56661726852</v>
+      </c>
+      <c r="E184" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>教育費（きょういくひ）</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>教育费</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>→ 教育費が高い。</t>
+        </is>
+      </c>
+      <c r="D185" s="1" t="n">
+        <v>46081.47182936343</v>
+      </c>
+      <c r="E185" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>暮らし（くらし）</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>生活</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>→ 田舎の暮らしは静かだ。</t>
+        </is>
+      </c>
+      <c r="D186" s="1" t="n">
+        <v>46083.45794787037</v>
+      </c>
+      <c r="E186" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>苦手（にがて）</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>不擅长的</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>→ 苦手なスポーツ。</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="n">
+        <v>46083.48571804398</v>
+      </c>
+      <c r="E187" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>細い（ほそい）</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>细的</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>→ 細い道。</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="n">
+        <v>46083.43499383102</v>
+      </c>
+      <c r="E188" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>要求する（ようきゅうする）</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>要求</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>→ 会社に説明を要求する。</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="n">
+        <v>46081.44741627315</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>大切（たいせつ）</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>重要的</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>→ 健康は大切だ。</t>
+        </is>
+      </c>
+      <c r="D190" s="1" t="n">
+        <v>46083.43565056713</v>
+      </c>
+      <c r="E190" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>飛ばす（とばす）</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>放飞/飞过</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>→ ボールを遠くに飛ばす。</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="n">
+        <v>46083.44739394676</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>暗い（くらい）</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>暗的</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>→ 暗い夜道。</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="n">
+        <v>46081.45056783565</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>撮る（とる）</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>拍摄</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>→ 写真を撮る。</t>
+        </is>
+      </c>
+      <c r="D193" s="1" t="n">
+        <v>46081.45060060185</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>犯罪（はんざい）</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>犯罪</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>→ 犯罪を防ぐための対策を取る。</t>
+        </is>
+      </c>
+      <c r="D194" s="1" t="n">
+        <v>46081.4779727662</v>
+      </c>
+      <c r="E194" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>入る（はいる）</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>进入</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>→ 部屋に入る。</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="n">
+        <v>46081.45100238426</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>上げる（あげる）</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>提高（他动）</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>→ 価格を上げる。</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="n">
+        <v>46083.4773046412</v>
+      </c>
+      <c r="E196" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ただちに</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>立即</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>→ ただちに対応する。</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="n">
+        <v>46083.45640927083</v>
+      </c>
+      <c r="E197" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>暑い（あつい）</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>热的（天气）</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>→ 暑い夏。</t>
+        </is>
+      </c>
+      <c r="D198" s="1" t="n">
+        <v>46081.45301979167</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>不十分（ふじゅうぶん）</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>不充分的</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>→ 不十分な準備。</t>
+        </is>
+      </c>
+      <c r="D199" s="1" t="n">
+        <v>46083.44402013889</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>許す（ゆるす）</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>原谅</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>→ 遅刻を許す。</t>
+        </is>
+      </c>
+      <c r="D200" s="1" t="n">
+        <v>46083.42913994213</v>
+      </c>
+      <c r="E200" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>難しい（むずかしい）</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>困难的</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>→ 難しい問題。</t>
+        </is>
+      </c>
+      <c r="D201" s="1" t="n">
+        <v>46083.45343956019</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>好きな（すきな）</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>喜欢（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" s="1" t="n">
+        <v>46081.4533702662</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>有名（ゆうめい）</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>有名的</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>→ 有名な作家。</t>
+        </is>
+      </c>
+      <c r="D203" s="1" t="n">
+        <v>46081.48778982639</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>不自然（ふしぜん）</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>不自然</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>→ 不自然な態度。</t>
+        </is>
+      </c>
+      <c r="D204" s="1" t="n">
+        <v>46081.4762840625</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>観察（かんさつ）</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>→ 子供の成長を観察する。</t>
+        </is>
+      </c>
+      <c r="D205" s="1" t="n">
+        <v>46081.55821111111</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>逃す（のがす）</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>错过</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>→ チャンスを逃す。</t>
+        </is>
+      </c>
+      <c r="D206" s="1" t="n">
+        <v>46083.45621270833</v>
+      </c>
+      <c r="E206" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>締切（しめきり）</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>截止</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>→ 締切は明日です。</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="n">
+        <v>46081.45371087963</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>回答（かいとう）</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>回答</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>→ すぐに回答してください。</t>
+        </is>
+      </c>
+      <c r="D208" s="1" t="n">
+        <v>46081.49790086805</v>
+      </c>
+      <c r="E208" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>休暇（きゅうか）</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>休假</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>→ 夏休みに休暇を取る。</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="n">
+        <v>46083.47363856481</v>
+      </c>
+      <c r="E209" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>見つける（みつける）</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>找到</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>→ 道に落ちた財布を見つける。</t>
+        </is>
+      </c>
+      <c r="D210" s="1" t="n">
+        <v>46083.44962302083</v>
+      </c>
+      <c r="E210" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>たとえ</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>即使/哪怕</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>→ たとえ雨でも行く。</t>
+        </is>
+      </c>
+      <c r="D211" s="1" t="n">
+        <v>46083.45755146991</v>
+      </c>
+      <c r="E211" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>紛争（ふんそう）</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>纷争</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>→ 地域紛争が起きている。</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="n">
+        <v>46081.64441328704</v>
+      </c>
+      <c r="E212" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>静か（しずか）</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>安静（※な形容词，已列后续）</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" s="1" t="n">
+        <v>46081.57145729167</v>
+      </c>
+      <c r="E213" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>増える（ふえる）</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>→ 外国人観光客が増えている。</t>
+        </is>
+      </c>
+      <c r="D214" s="1" t="n">
+        <v>46083.43688530093</v>
+      </c>
+      <c r="E214" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>探す（さがす）</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>寻找</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>→ 道に落ちた財布を探す。</t>
+        </is>
+      </c>
+      <c r="D215" s="1" t="n">
+        <v>46083.45250783565</v>
+      </c>
+      <c r="E215" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>予定する（よていする）</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>预定</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>→ 会議を予定する。</t>
+        </is>
+      </c>
+      <c r="D216" s="1" t="n">
+        <v>46083.44986353009</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>悲しい（かなしい）</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>悲伤的</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>→ 悲しいニュースを聞いた。</t>
+        </is>
+      </c>
+      <c r="D217" s="1" t="n">
+        <v>46081.60799597222</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>増加する（ぞうかする）</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>→ 人口が増加する。</t>
+        </is>
+      </c>
+      <c r="D218" s="1" t="n">
+        <v>46083.47764173611</v>
+      </c>
+      <c r="E218" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>集まる（あつまる）</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>聚集（自动）</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>→ 人々が集まる。</t>
+        </is>
+      </c>
+      <c r="D219" s="1" t="n">
+        <v>46081.62917052084</v>
+      </c>
+      <c r="E219" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>不利（ふり）</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>不利的</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>→ 不利な立場。</t>
+        </is>
+      </c>
+      <c r="D220" s="1" t="n">
+        <v>46083.44194229167</v>
+      </c>
+      <c r="E220" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>続出する（ぞくしゅつする）</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>接连出现</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>→ 問題が続出している。</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="n">
+        <v>46083.44993398148</v>
+      </c>
+      <c r="E221" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>得る（える）</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>获得</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>→ 経験を得る。</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="n">
+        <v>46083.47822619213</v>
+      </c>
+      <c r="E222" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>経験者（けいけんしゃ）</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>有经验者</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>→ 経験者を募集している。</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="n">
+        <v>46081.57611826389</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>季節（きせつ）</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>季节</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>→ 日本には四季がある。</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="n">
+        <v>46083.48607865741</v>
+      </c>
+      <c r="E224" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>だからこそ</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>正因为如此</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>→ 大変だった。だからこそ、成長できた。</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="n">
+        <v>46083.44894658565</v>
+      </c>
+      <c r="E225" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>速い（はやい）</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>快的</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>→ 車が速い。</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="n">
+        <v>46081.60948157407</v>
+      </c>
+      <c r="E226" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>または</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>或者</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>→ バス、または電車で行く。</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="n">
+        <v>46083.44901428241</v>
+      </c>
+      <c r="E227" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>降りる（おりる）</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>下车</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>→ 駅で降りる。</t>
+        </is>
+      </c>
+      <c r="D228" s="1" t="n">
+        <v>46083.4502281713</v>
+      </c>
+      <c r="E228" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>調べる（しらべる）</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>调查</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>→ インターネットで調べる。</t>
+        </is>
+      </c>
+      <c r="D229" s="1" t="n">
+        <v>46081.60811952547</v>
+      </c>
+      <c r="E229" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>操作（そうさ）</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>→ 機械の操作は簡単だ。</t>
+        </is>
+      </c>
+      <c r="D230" s="1" t="n">
+        <v>46081.57768496528</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>偉い（えらい）</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>了不起的/了得的</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>→ 偉い先生。</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="n">
+        <v>46083.47514553241</v>
+      </c>
+      <c r="E231" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>預ける（あずける）</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>托付</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>→ 荷物を預ける。</t>
+        </is>
+      </c>
+      <c r="D232" s="1" t="n">
+        <v>46081.57845755787</v>
+      </c>
+      <c r="E232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>回復する（かいふくする）</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>恢复</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>→ 体力が回復する。</t>
+        </is>
+      </c>
+      <c r="D233" s="1" t="n">
+        <v>46081.61149313657</v>
+      </c>
+      <c r="E233" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>もちろん</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>当然</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>→ もちろん行く。</t>
+        </is>
+      </c>
+      <c r="D234" s="1" t="n">
+        <v>46083.48510135417</v>
+      </c>
+      <c r="E234" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>しっかり</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>踏实</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>→ しっかり握る。</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="n">
+        <v>46083.45859837963</v>
+      </c>
+      <c r="E235" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>平等（びょうどう）</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>平等的（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" s="1" t="n">
+        <v>46083.45955703704</v>
+      </c>
+      <c r="E236" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>丁寧な（ていねいな）</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>礼貌的（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" s="1" t="n">
+        <v>46083.45744444444</v>
+      </c>
+      <c r="E237" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>応援する（おうえんする）</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>支持/加油</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>→ チームを応援する。</t>
+        </is>
+      </c>
+      <c r="D238" s="1" t="n">
+        <v>46081.62857184028</v>
+      </c>
+      <c r="E238" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>上がる（あがる）</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>→ 売上が上がる。</t>
+        </is>
+      </c>
+      <c r="D239" s="1" t="n">
+        <v>46083.43605648148</v>
+      </c>
+      <c r="E239" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>直る（なおる）</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>修好（自动）</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>→ 壊れた時計が直った。</t>
+        </is>
+      </c>
+      <c r="D240" s="1" t="n">
+        <v>46081.6434546875</v>
+      </c>
+      <c r="E240" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>捜す（さがす）</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>搜寻</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>→ 犯人を捜す。</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="n">
+        <v>46083.45966958333</v>
+      </c>
+      <c r="E241" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>決まる（きまる）</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>决定（自动）</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>→ 日程が決まった。</t>
+        </is>
+      </c>
+      <c r="D242" s="1" t="n">
+        <v>46081.57978359954</v>
+      </c>
+      <c r="E242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>きちんと</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>整齐/确实</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>→ きちんと並べる。</t>
+        </is>
+      </c>
+      <c r="D243" s="1" t="n">
+        <v>46083.45653466435</v>
+      </c>
+      <c r="E243" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>成功する（せいこうする）</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>→ 計画が成功する。</t>
+        </is>
+      </c>
+      <c r="D244" s="1" t="n">
+        <v>46083.45934130787</v>
+      </c>
+      <c r="E244" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>下げる（さげる）</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>降低</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>→ 温度を下げる。</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="n">
+        <v>46081.61025388889</v>
+      </c>
+      <c r="E245" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>修正（しゅうせい）</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>修改</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>→ 間違いを修正する。</t>
+        </is>
+      </c>
+      <c r="D246" s="1" t="n">
+        <v>46081.58035614583</v>
+      </c>
+      <c r="E246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>じつに（実に）</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>非常/确实</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>→ 実に素晴らしい。</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="n">
+        <v>46083.47599181713</v>
+      </c>
+      <c r="E247" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>便利（べんり）</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>方便的</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>→ この道具は便利だ。</t>
+        </is>
+      </c>
+      <c r="D248" s="1" t="n">
+        <v>46083.47750820602</v>
+      </c>
+      <c r="E248" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>出勤（しゅっきん）</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>上班</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>→ 毎朝8時に出勤する。</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="n">
+        <v>46081.64536541667</v>
+      </c>
+      <c r="E249" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>実行する（じっこうする）</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>实行</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>→ 計画を実行する。</t>
+        </is>
+      </c>
+      <c r="D250" s="1" t="n">
+        <v>46081.58077465278</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>信用（しんよう）</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>信用</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>→ 信用を失う。</t>
+        </is>
+      </c>
+      <c r="D251" s="1" t="n">
+        <v>46081.60609060185</v>
+      </c>
+      <c r="E251" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>収支（しゅうし）</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>收支</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>→ 収支のバランスを取る。</t>
+        </is>
+      </c>
+      <c r="D252" s="1" t="n">
+        <v>46081.58083803241</v>
+      </c>
+      <c r="E252" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>割合（わりあい）</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>比例</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>→ 女性の割合が増えている。</t>
+        </is>
+      </c>
+      <c r="D253" s="1" t="n">
+        <v>46081.58084825231</v>
+      </c>
+      <c r="E253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>不正確（ふせいかく）</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>不准确</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>→ 不正確な記録。</t>
+        </is>
+      </c>
+      <c r="D254" s="1" t="n">
+        <v>46081.64481056713</v>
+      </c>
+      <c r="E254" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>性格（せいかく）</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>性格</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>→ 彼は明るい性格だ。</t>
+        </is>
+      </c>
+      <c r="D255" s="1" t="n">
+        <v>46083.4565078125</v>
+      </c>
+      <c r="E255" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>生産（せいさん）</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>生产</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>→ 自動車の生産が増加した。</t>
+        </is>
+      </c>
+      <c r="D256" s="1" t="n">
+        <v>46083.45855899306</v>
+      </c>
+      <c r="E256" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>単純な（たんじゅんな）</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>单纯/简单（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" s="1" t="n">
+        <v>46083.4770515162</v>
+      </c>
+      <c r="E257" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>記事（きじ）</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>报道/文章</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>→ 新聞の記事を読む。</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="n">
+        <v>46083.48040314815</v>
+      </c>
+      <c r="E258" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>開発（かいはつ）</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>开发</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>→ 新しい技術を開発する。</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="n">
+        <v>46083.48261077546</v>
+      </c>
+      <c r="E259" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>燃える（もえる）</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>燃烧</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>→ 木が燃える。</t>
+        </is>
+      </c>
+      <c r="D260" s="1" t="n">
+        <v>46083.4826590162</v>
+      </c>
+      <c r="E260" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>しかも</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>而且/并且</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>→ 安い。しかも美味しい。</t>
+        </is>
+      </c>
+      <c r="D261" s="1" t="n">
+        <v>46083.60148481481</v>
+      </c>
+      <c r="E261" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>割れる（われる）</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>破裂</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>→ コップが割れる。</t>
+        </is>
+      </c>
+      <c r="D262" s="1" t="n">
+        <v>46083.49470054398</v>
+      </c>
+      <c r="E262" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>安全（あんぜん）</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>安全的</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>→ 安全な場所。</t>
+        </is>
+      </c>
+      <c r="D263" s="1" t="n">
+        <v>46083.58028030093</v>
+      </c>
+      <c r="E263" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>出発（しゅっぱつ）</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>出发</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>→ 朝早く出発する。</t>
+        </is>
+      </c>
+      <c r="D264" s="1" t="n">
+        <v>46083.49496636574</v>
+      </c>
+      <c r="E264" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>つい</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>无意间</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>→ つい手を出してしまった。</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="n">
+        <v>46083.6015534375</v>
+      </c>
+      <c r="E265" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>送る（おくる）</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>送</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>→ メールを送る。</t>
+        </is>
+      </c>
+      <c r="D266" s="1" t="n">
+        <v>46083.59968177084</v>
+      </c>
+      <c r="E266" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>役割（やくわり）</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>作用/角色</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>→ 彼は重要な役割を果たした。</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="n">
+        <v>46083.49524334491</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>病気（びょうき）</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>生病的</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>→ 病気の犬。</t>
+        </is>
+      </c>
+      <c r="D268" s="1" t="n">
+        <v>46083.49534628472</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>競争（きょうそう）</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>竞争</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>→ 激しい競争が続いている。</t>
+        </is>
+      </c>
+      <c r="D269" s="1" t="n">
+        <v>46083.60015309028</v>
+      </c>
+      <c r="E269" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>契約書（けいやくしょ）</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>合同书</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>→ 契約書にサインする。</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="n">
+        <v>46083.49575646991</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>いくつか</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>几个</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>→ いくつか質問がある。</t>
+        </is>
+      </c>
+      <c r="D271" s="1" t="n">
+        <v>46083.49581480324</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>意見（いけん）</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>意见</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>→ 意見を述べる。</t>
+        </is>
+      </c>
+      <c r="D272" s="1" t="n">
+        <v>46083.49589113426</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>回る（まわる）</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>转动/巡回</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>→ 時計の針が回る。</t>
+        </is>
+      </c>
+      <c r="D273" s="1" t="n">
+        <v>46083.62302114583</v>
+      </c>
+      <c r="E273" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>不健康（ふけんこう）</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>不健康的</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>→ 不健康な食生活。</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="n">
+        <v>46083.58114829861</v>
+      </c>
+      <c r="E274" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>負ける（まける）</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>输</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>→ 試合に負けた。</t>
+        </is>
+      </c>
+      <c r="D275" s="1" t="n">
+        <v>46083.60113050926</v>
+      </c>
+      <c r="E275" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>いっぱい</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>满/很多</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>→ 部屋がいっぱいだ。</t>
+        </is>
+      </c>
+      <c r="D276" s="1" t="n">
+        <v>46083.57926170139</v>
+      </c>
+      <c r="E276" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>壊れる（こわれる）</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>坏掉（自动）</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>→ 椅子が壊れた。</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="n">
+        <v>46083.49722420139</v>
+      </c>
+      <c r="E277" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>不丁寧な（ふていねいな）</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>不礼貌（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" s="1" t="n">
+        <v>46083.61144454861</v>
+      </c>
+      <c r="E278" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>欠勤（けっきん）</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>缺勤</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>→ 体調不良で欠勤した。</t>
+        </is>
+      </c>
+      <c r="D279" s="1" t="n">
+        <v>46083.49738641204</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>易しい（やさしい）</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>容易/亲切</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>→ 問題が易しい。</t>
+        </is>
+      </c>
+      <c r="D280" s="1" t="n">
+        <v>46083.49745451389</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>割れる（われる）</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>破碎（自动）</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>→ コップが割れた。</t>
+        </is>
+      </c>
+      <c r="D281" s="1" t="n">
+        <v>46083.49753841435</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>ときどき</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>有时</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>→ ときどき映画を見る。</t>
+        </is>
+      </c>
+      <c r="D282" s="1" t="n">
+        <v>46083.49761341435</v>
+      </c>
+      <c r="E282" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>正確（せいかく）</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>准确的</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>→ 正確な情報。</t>
+        </is>
+      </c>
+      <c r="D283" s="1" t="n">
+        <v>46083.60178751157</v>
+      </c>
+      <c r="E283" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>いずれ</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>终将/不久</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>→ いずれ分かる。</t>
+        </is>
+      </c>
+      <c r="D284" s="1" t="n">
+        <v>46083.49771384259</v>
+      </c>
+      <c r="E284" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>脱出する（だっしゅつする）</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>逃脱</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>→ 火事から脱出する。</t>
+        </is>
+      </c>
+      <c r="D285" s="1" t="n">
+        <v>46083.61983996528</v>
+      </c>
+      <c r="E285" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>穏やか（おだやか）</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>平稳/温和（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" s="1" t="n">
+        <v>46083.62463166667</v>
+      </c>
+      <c r="E286" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>農業（のうぎょう）</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>农业</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>→ 農業に従事している。</t>
+        </is>
+      </c>
+      <c r="D287" s="1" t="n">
+        <v>46083.49778431713</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>素敵（すてき）</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>极好的</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>→ 素敵な服。</t>
+        </is>
+      </c>
+      <c r="D288" s="1" t="n">
+        <v>46083.62241533565</v>
+      </c>
+      <c r="E288" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>運動（うんどう）</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>运动</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>→ 毎日運動している。</t>
+        </is>
+      </c>
+      <c r="D289" s="1" t="n">
+        <v>46083.49778832176</v>
+      </c>
+      <c r="E289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>影響する（えいきょうする）</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>影响</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>→ 天候が農作物に影響する。</t>
+        </is>
+      </c>
+      <c r="D290" s="1" t="n">
+        <v>46083.5987790625</v>
+      </c>
+      <c r="E290" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>進む（すすむ）</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>进行（自动）</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>→ 仕事が順調に進む。</t>
+        </is>
+      </c>
+      <c r="D291" s="1" t="n">
+        <v>46083.59859663194</v>
+      </c>
+      <c r="E291" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>維持する（いじする）</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>维持</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>→ 健康を維持する。</t>
+        </is>
+      </c>
+      <c r="D292" s="1" t="n">
+        <v>46083.59885408565</v>
+      </c>
+      <c r="E292" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>休日（きゅうじつ）</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>休息日</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>→ 休日は家でゆっくりする。</t>
+        </is>
+      </c>
+      <c r="D293" s="1" t="n">
+        <v>46083.60192181713</v>
+      </c>
+      <c r="E293" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>不正確な（ふせいかくな）</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>不准确（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" s="1" t="n">
+        <v>46083.60007153935</v>
+      </c>
+      <c r="E294" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>消える（きえる）</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>消失</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>→ 電気が消えた。</t>
+        </is>
+      </c>
+      <c r="D295" s="1" t="n">
+        <v>46083.62258003472</v>
+      </c>
+      <c r="E295" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>活発（かっぱつ）</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>活跃的（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" s="1" t="n">
+        <v>46083.62155858796</v>
+      </c>
+      <c r="E296" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>調整する（ちょうせいする）</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>→ スケジュールを調整する。</t>
+        </is>
+      </c>
+      <c r="D297" s="1" t="n">
+        <v>46083.60065891204</v>
+      </c>
+      <c r="E297" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>必要（ひつよう）</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>必要的</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>→ 必要な物。</t>
+        </is>
+      </c>
+      <c r="D298" s="1" t="n">
+        <v>46083.49782516203</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>つまり</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>换句话说</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>→ つまり、失敗したということだ。</t>
+        </is>
+      </c>
+      <c r="D299" s="1" t="n">
+        <v>46083.49783634259</v>
+      </c>
+      <c r="E299" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>壊れる（こわれる）</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>坏掉</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>→ 椅子が壊れる。</t>
+        </is>
+      </c>
+      <c r="D300" s="1" t="n">
+        <v>46083.59745643519</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>易しい（やさしい）</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>简单的/温柔的</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>→ 易しい問題。</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="n">
+        <v>46083.59950416667</v>
+      </c>
+      <c r="E301" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>とにかく</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>总之/不管怎样</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>→ とにかく行ってみよう。</t>
+        </is>
+      </c>
+      <c r="D302" s="1" t="n">
+        <v>46083.63636667824</v>
+      </c>
+      <c r="E302" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>関わる（かかわる）</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>涉及</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>→ 環境問題に関わる仕事。</t>
+        </is>
+      </c>
+      <c r="D303" s="1" t="n">
+        <v>46083.68089658565</v>
+      </c>
+      <c r="E303" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>元気（げんき）</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>精神/健康的</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>→ 元気な子供。</t>
+        </is>
+      </c>
+      <c r="D304" s="1" t="n">
+        <v>46083.63942392361</v>
+      </c>
+      <c r="E304" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>折れる（おれる）</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>折断（自动）</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>→ 木の枝が折れた。</t>
+        </is>
+      </c>
+      <c r="D305" s="1" t="n">
+        <v>46083.6407237963</v>
+      </c>
+      <c r="E305" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>ほんの</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>仅仅</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>→ ほんの少し。</t>
+        </is>
+      </c>
+      <c r="D306" s="1" t="n">
+        <v>46083.68111403276</v>
+      </c>
+      <c r="E306" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>わざと</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>故意</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>→ わざと落とす。</t>
+        </is>
+      </c>
+      <c r="D307" s="1" t="n">
+        <v>46083.67786315972</v>
+      </c>
+      <c r="E307" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>柔らかい（やわらかい）</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>软的</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>→ 柔らかいクッション。</t>
+        </is>
+      </c>
+      <c r="D308" s="1" t="n">
+        <v>46083.67986309028</v>
+      </c>
+      <c r="E308" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>すでに</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>已经</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>→ すでに決まっている。</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="n">
+        <v>46083.64110103009</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>なぜなら</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>因为</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>→ 行けない。なぜなら忙しいからだ。</t>
+        </is>
+      </c>
+      <c r="D310" s="1" t="n">
+        <v>46083.64113903936</v>
+      </c>
+      <c r="E310" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>処理（しょり）</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>处理</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>→ データを処理する。</t>
+        </is>
+      </c>
+      <c r="D311" s="1" t="n">
+        <v>46083.64162704861</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>判決（はんけつ）</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>判决</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>→ 判決が下された。</t>
+        </is>
+      </c>
+      <c r="D312" s="1" t="n">
+        <v>46083.64177202546</v>
+      </c>
+      <c r="E312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>協力（きょうりょく）</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>合作</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>→ 協力して問題を解決する。</t>
+        </is>
+      </c>
+      <c r="D313" s="1" t="n">
+        <v>46083.67872515046</v>
+      </c>
+      <c r="E313" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>環境保護（かんきょうほご）</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>环境保护</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>→ 環境保護に取り組む。</t>
+        </is>
+      </c>
+      <c r="D314" s="1" t="n">
+        <v>46083.64224572917</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>看護（かんご）</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>护理</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>→ 看護の仕事をしている。</t>
+        </is>
+      </c>
+      <c r="D315" s="1" t="n">
+        <v>46083.67895589121</v>
+      </c>
+      <c r="E315" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>関係（かんけい）</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>关系</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>→ 両国の関係が改善した。</t>
+        </is>
+      </c>
+      <c r="D316" s="1" t="n">
+        <v>46083.64306090278</v>
+      </c>
+      <c r="E316" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>もっとも</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>不过/然而</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>→ 便利だ。もっとも高いけど。</t>
+        </is>
+      </c>
+      <c r="D317" s="1" t="n">
+        <v>46083.64315153935</v>
+      </c>
+      <c r="E317" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>どんどん</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>迅速/不断</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>→ どんどん進む。</t>
+        </is>
+      </c>
+      <c r="D318" s="1" t="n">
+        <v>46083.64341861111</v>
+      </c>
+      <c r="E318" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>台風（たいふう）</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>台风</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>→ 台風が近づいている。</t>
+        </is>
+      </c>
+      <c r="D319" s="1" t="n">
+        <v>46083.64343747685</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>渡す（わたす）</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>交给</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>→ 書類を渡す。</t>
+        </is>
+      </c>
+      <c r="D320" s="1" t="n">
+        <v>46083.64364195602</v>
+      </c>
+      <c r="E320" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>需要（じゅよう）</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>需求</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>→ 需要が高まっている。</t>
+        </is>
+      </c>
+      <c r="D321" s="1" t="n">
+        <v>46083.644015625</v>
+      </c>
+      <c r="E321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>予約（よやく）</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>预约</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>→ レストランを予約する。</t>
+        </is>
+      </c>
+      <c r="D322" s="1" t="n">
+        <v>46083.64453472223</v>
+      </c>
+      <c r="E322" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>出る（でる）</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>出去/出现</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>→ 会議に出る。</t>
+        </is>
+      </c>
+      <c r="D323" s="1" t="n">
+        <v>46083.64475981482</v>
+      </c>
+      <c r="E323" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>解決策（かいけつさく）</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>解决对策</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>→ 解決策を考える。</t>
+        </is>
+      </c>
+      <c r="D324" s="1" t="n">
+        <v>46083.64494649306</v>
+      </c>
+      <c r="E324" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>下がる（さがる）</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>下降</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>→ 気温が下がる。</t>
+        </is>
+      </c>
+      <c r="D325" s="1" t="n">
+        <v>46083.64520998843</v>
+      </c>
+      <c r="E325" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>続ける（つづける）</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>继续</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>→ 日本語の勉強を続けている。</t>
+        </is>
+      </c>
+      <c r="D326" s="1" t="n">
+        <v>46083.6454000463</v>
+      </c>
+      <c r="E326" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>昇進（しょうしん）</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>升职</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>→ 彼は昇進した。</t>
+        </is>
+      </c>
+      <c r="D327" s="1" t="n">
+        <v>46083.67888483797</v>
+      </c>
+      <c r="E327" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>勝つ（かつ）</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>赢</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>→ 試合に勝つ。</t>
+        </is>
+      </c>
+      <c r="D328" s="1" t="n">
+        <v>46083.67526832176</v>
+      </c>
+      <c r="E328" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>親子（おやこ）</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>亲子</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>→ 親子の関係が良い。</t>
+        </is>
+      </c>
+      <c r="D329" s="1" t="n">
+        <v>46083.64618262732</v>
+      </c>
+      <c r="E329" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>素敵な（すてきな）</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>极好（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" s="1" t="n">
+        <v>46083.64661519676</v>
+      </c>
+      <c r="E330" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>合格（ごうかく）</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>→ 試験に合格した。</t>
+        </is>
+      </c>
+      <c r="D331" s="1" t="n">
+        <v>46083.64682537037</v>
+      </c>
+      <c r="E331" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>会議（かいぎ）</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>会议</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>→ 会議に参加する。</t>
+        </is>
+      </c>
+      <c r="D332" s="1" t="n">
+        <v>46083.64697675926</v>
+      </c>
+      <c r="E332" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>冷やす（ひやす）</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>冷却</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>→ 水で体を冷やす。</t>
+        </is>
+      </c>
+      <c r="D333" s="1" t="n">
+        <v>46083.68067733796</v>
+      </c>
+      <c r="E333" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>まさか</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>难道/不会吧</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>→ まさかそんなことが。</t>
+        </is>
+      </c>
+      <c r="D334" s="1" t="n">
+        <v>46083.64710584491</v>
+      </c>
+      <c r="E334" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>組合（くみあい）</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>工会/组合</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>→ 労働組合に入っている。</t>
+        </is>
+      </c>
+      <c r="D335" s="1" t="n">
+        <v>46083.64732326389</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>美しい（うつくしい）</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>美丽的（※也可作い形容词）</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>→ 美しい景色。</t>
+        </is>
+      </c>
+      <c r="D336" s="1" t="n">
+        <v>46083.64751833333</v>
+      </c>
+      <c r="E336" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>通る（とおる）</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>→ 道を通る。</t>
+        </is>
+      </c>
+      <c r="D337" s="1" t="n">
+        <v>46083.64779376157</v>
+      </c>
+      <c r="E337" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>折れる（おれる）</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>折断</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>→ 木の枝が折れる。</t>
+        </is>
+      </c>
+      <c r="D338" s="1" t="n">
+        <v>46083.6762387037</v>
+      </c>
+      <c r="E338" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>どんどん</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>迅速/连续</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>→ どんどん進める。</t>
+        </is>
+      </c>
+      <c r="D339" s="1" t="n">
+        <v>46083.67841535879</v>
+      </c>
+      <c r="E339" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/wrong_words.xlsx
+++ b/wrong_words.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E339"/>
+  <dimension ref="A1:E426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,10 +631,10 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" s="1" t="n">
-        <v>46080.46550108797</v>
+        <v>46084.74288440972</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -745,10 +745,10 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" s="1" t="n">
-        <v>46080.46664003472</v>
+        <v>46084.71490069445</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1030,10 +1030,10 @@
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" s="1" t="n">
-        <v>46080.69804697917</v>
+        <v>46084.43552594908</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -1163,10 +1163,10 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" s="1" t="n">
-        <v>46083.45678017361</v>
+        <v>46084.38787023148</v>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -1201,10 +1201,10 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" s="1" t="n">
-        <v>46080.46668291667</v>
+        <v>46084.5828346875</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1239,10 +1239,10 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" s="1" t="n">
-        <v>46083.45132778935</v>
+        <v>46084.44049435185</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1277,10 +1277,10 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" s="1" t="n">
-        <v>46080.46669075231</v>
+        <v>46084.62936355324</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1315,10 +1315,10 @@
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" s="1" t="n">
-        <v>46083.59788269676</v>
+        <v>46084.45916077546</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1486,10 +1486,10 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" s="1" t="n">
-        <v>46080.46671119213</v>
+        <v>46084.56974348379</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46080.5639512037</v>
+        <v>46084.55556179398</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46080.56526182871</v>
+        <v>46084.43941619213</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46080.56577579861</v>
+        <v>46084.481588125</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46080.56806637732</v>
+        <v>46084.55703967593</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46080.56894141204</v>
+        <v>46084.55483743056</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46080.57033020833</v>
+        <v>46084.55358927084</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46080.57461549769</v>
+        <v>46084.48149962963</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46080.61294725694</v>
+        <v>46084.46704262732</v>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46080.61464663195</v>
+        <v>46084.478388125</v>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46080.70094481482</v>
+        <v>46084.43805354166</v>
       </c>
       <c r="E138" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46080.61549799769</v>
+        <v>46084.48272568287</v>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46080.67273118056</v>
+        <v>46084.44076814815</v>
       </c>
       <c r="E140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46083.48602541666</v>
+        <v>46084.43536424769</v>
       </c>
       <c r="E147" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148">
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46080.68646912037</v>
+        <v>46084.46197811342</v>
       </c>
       <c r="E151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152">
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46080.67791672454</v>
+        <v>46084.46105616898</v>
       </c>
       <c r="E152" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46080.67439758102</v>
+        <v>46084.4738137963</v>
       </c>
       <c r="E158" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159">
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46080.68578065973</v>
+        <v>46084.48050651621</v>
       </c>
       <c r="E159" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160">
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46080.68632105324</v>
+        <v>46084.46115052083</v>
       </c>
       <c r="E163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -3934,10 +3934,10 @@
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" s="1" t="n">
-        <v>46080.69992422454</v>
+        <v>46084.38639787037</v>
       </c>
       <c r="E164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165">
@@ -4091,10 +4091,10 @@
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" s="1" t="n">
-        <v>46083.43668841435</v>
+        <v>46084.57232057871</v>
       </c>
       <c r="E171" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172">
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46083.48571804398</v>
+        <v>46084.4390068287</v>
       </c>
       <c r="E187" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188">
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46083.43565056713</v>
+        <v>46084.38675277778</v>
       </c>
       <c r="E190" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="191">
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46083.4773046412</v>
+        <v>46084.43992134259</v>
       </c>
       <c r="E196" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197">
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46083.45640927083</v>
+        <v>46084.3858132176</v>
       </c>
       <c r="E197" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198">
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46083.44402013889</v>
+        <v>46084.45494427083</v>
       </c>
       <c r="E199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200">
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46083.45621270833</v>
+        <v>46084.38930721065</v>
       </c>
       <c r="E206" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207">
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46083.44962302083</v>
+        <v>46084.45342024306</v>
       </c>
       <c r="E210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211">
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46083.45250783565</v>
+        <v>46084.38716023148</v>
       </c>
       <c r="E215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216">
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46083.48607865741</v>
+        <v>46084.42184180555</v>
       </c>
       <c r="E224" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225">
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46083.47750820602</v>
+        <v>46084.46081677084</v>
       </c>
       <c r="E248" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249">
@@ -6026,10 +6026,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46083.45855899306</v>
+        <v>46084.46866521991</v>
       </c>
       <c r="E256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>46083.49470054398</v>
+        <v>46084.46436883102</v>
       </c>
       <c r="E262" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263">
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>46083.60015309028</v>
+        <v>46084.46679207176</v>
       </c>
       <c r="E269" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="270">
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>46083.62302114583</v>
+        <v>46084.544113125</v>
       </c>
       <c r="E273" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="274">
@@ -6482,10 +6482,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>46083.57926170139</v>
+        <v>46084.46042354167</v>
       </c>
       <c r="E276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>46083.49771384259</v>
+        <v>46084.54716353009</v>
       </c>
       <c r="E284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285">
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>46083.61983996528</v>
+        <v>46084.44225155093</v>
       </c>
       <c r="E285" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="286">
@@ -6704,10 +6704,10 @@
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" s="1" t="n">
-        <v>46083.62463166667</v>
+        <v>46084.45362160879</v>
       </c>
       <c r="E286" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="287">
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>46083.59859663194</v>
+        <v>46084.48280818287</v>
       </c>
       <c r="E291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -6926,10 +6926,10 @@
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" s="1" t="n">
-        <v>46083.62155858796</v>
+        <v>46084.43450782407</v>
       </c>
       <c r="E296" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="297">
@@ -6995,10 +6995,10 @@
         </is>
       </c>
       <c r="D299" s="1" t="n">
-        <v>46083.49783634259</v>
+        <v>46084.54533444445</v>
       </c>
       <c r="E299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D300" s="1" t="n">
-        <v>46083.59745643519</v>
+        <v>46084.46055318287</v>
       </c>
       <c r="E300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="D306" s="1" t="n">
-        <v>46083.68111403276</v>
+        <v>46084.43961734954</v>
       </c>
       <c r="E306" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="307">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D307" s="1" t="n">
-        <v>46083.67786315972</v>
+        <v>46084.46246259259</v>
       </c>
       <c r="E307" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308">
@@ -7202,10 +7202,10 @@
         </is>
       </c>
       <c r="D308" s="1" t="n">
-        <v>46083.67986309028</v>
+        <v>46084.47725706019</v>
       </c>
       <c r="E308" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="309">
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="D309" s="1" t="n">
-        <v>46083.64110103009</v>
+        <v>46084.54694444445</v>
       </c>
       <c r="E309" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310">
@@ -7317,10 +7317,10 @@
         </is>
       </c>
       <c r="D313" s="1" t="n">
-        <v>46083.67872515046</v>
+        <v>46084.47931846065</v>
       </c>
       <c r="E313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="D317" s="1" t="n">
-        <v>46083.64315153935</v>
+        <v>46084.56998149306</v>
       </c>
       <c r="E317" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="318">
@@ -7501,10 +7501,10 @@
         </is>
       </c>
       <c r="D321" s="1" t="n">
-        <v>46083.644015625</v>
+        <v>46084.55636740741</v>
       </c>
       <c r="E321" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322">
@@ -7524,10 +7524,10 @@
         </is>
       </c>
       <c r="D322" s="1" t="n">
-        <v>46083.64453472223</v>
+        <v>46084.54846237269</v>
       </c>
       <c r="E322" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323">
@@ -7704,10 +7704,10 @@
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" s="1" t="n">
-        <v>46083.64661519676</v>
+        <v>46084.5720059838</v>
       </c>
       <c r="E330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="D333" s="1" t="n">
-        <v>46083.68067733796</v>
+        <v>46084.44121475695</v>
       </c>
       <c r="E333" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="334">
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="D338" s="1" t="n">
-        <v>46083.6762387037</v>
+        <v>46084.47411228009</v>
       </c>
       <c r="E338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339">
@@ -7914,6 +7914,2003 @@
         <v>46083.67841535879</v>
       </c>
       <c r="E339" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>影響（えいきょう）</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>影响</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>→ 天候は農業に大きな影響を与える。</t>
+        </is>
+      </c>
+      <c r="D340" s="1" t="n">
+        <v>46084.55068954861</v>
+      </c>
+      <c r="E340" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>現象（げんしょう）</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>现象</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>→ 最近、異常気象の現象が増えている。</t>
+        </is>
+      </c>
+      <c r="D341" s="1" t="n">
+        <v>46084.57270822916</v>
+      </c>
+      <c r="E341" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>印象（いんしょう）</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>印象</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>→ 強い印象を受けた。</t>
+        </is>
+      </c>
+      <c r="D342" s="1" t="n">
+        <v>46084.55295421297</v>
+      </c>
+      <c r="E342" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>環境（かんきょう）</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>环境</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>→ 自然環境を守る。</t>
+        </is>
+      </c>
+      <c r="D343" s="1" t="n">
+        <v>46084.57044366898</v>
+      </c>
+      <c r="E343" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>不安（ふあん）</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>不安</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>→ 将来に不安を感じる。</t>
+        </is>
+      </c>
+      <c r="D344" s="1" t="n">
+        <v>46084.57174799769</v>
+      </c>
+      <c r="E344" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>故障（こしょう）</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>故障</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>→ 機械が故障した。</t>
+        </is>
+      </c>
+      <c r="D345" s="1" t="n">
+        <v>46084.57260583333</v>
+      </c>
+      <c r="E345" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>立派（りっぱ）</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>了不起的</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>→ 立派な建物。</t>
+        </is>
+      </c>
+      <c r="D346" s="1" t="n">
+        <v>46084.5768980787</v>
+      </c>
+      <c r="E346" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>寒い（さむい）</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>冷的（天气）</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>→ 寒い冬。</t>
+        </is>
+      </c>
+      <c r="D347" s="1" t="n">
+        <v>46084.57725140046</v>
+      </c>
+      <c r="E347" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>間違い（まちがい）</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>错误的</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>→ 間違いのない文章。</t>
+        </is>
+      </c>
+      <c r="D348" s="1" t="n">
+        <v>46084.63159563657</v>
+      </c>
+      <c r="E348" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>改善（かいぜん）</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>改善</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>→ 問題を改善する必要がある。</t>
+        </is>
+      </c>
+      <c r="D349" s="1" t="n">
+        <v>46084.64670519676</v>
+      </c>
+      <c r="E349" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>返す（かえす）</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>归还</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>→ 借りた本を返す。</t>
+        </is>
+      </c>
+      <c r="D350" s="1" t="n">
+        <v>46084.62577748843</v>
+      </c>
+      <c r="E350" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>不明確（ふめいかく）</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>不明确的（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" s="1" t="n">
+        <v>46084.63190570602</v>
+      </c>
+      <c r="E351" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>避ける（さける）</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>避免</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>→ 危険を避ける。</t>
+        </is>
+      </c>
+      <c r="D352" s="1" t="n">
+        <v>46084.71062622685</v>
+      </c>
+      <c r="E352" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>保つ（たもつ）</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>保持</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>→ 健康を保つ。</t>
+        </is>
+      </c>
+      <c r="D353" s="1" t="n">
+        <v>46084.70124829861</v>
+      </c>
+      <c r="E353" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>苦い（にがい）</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>苦的</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>→ コーヒーは苦い。</t>
+        </is>
+      </c>
+      <c r="D354" s="1" t="n">
+        <v>46084.57865244213</v>
+      </c>
+      <c r="E354" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>機関（きかん）</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>机关/机构</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>→ 政府機関に勤めている。</t>
+        </is>
+      </c>
+      <c r="D355" s="1" t="n">
+        <v>46084.57875827546</v>
+      </c>
+      <c r="E355" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>入社（にゅうしゃ）</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>→ 来月入社する。</t>
+        </is>
+      </c>
+      <c r="D356" s="1" t="n">
+        <v>46084.57928957176</v>
+      </c>
+      <c r="E356" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>たまたま</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>碰巧</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>→ たまたま会った。</t>
+        </is>
+      </c>
+      <c r="D357" s="1" t="n">
+        <v>46084.57974817129</v>
+      </c>
+      <c r="E357" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>快適（かいてき）</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>舒适的</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>→ 快適な部屋。</t>
+        </is>
+      </c>
+      <c r="D358" s="1" t="n">
+        <v>46084.70137322917</v>
+      </c>
+      <c r="E358" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>緊張（きんちょう）</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>紧张</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>→ 面接で緊張した。</t>
+        </is>
+      </c>
+      <c r="D359" s="1" t="n">
+        <v>46084.58018053241</v>
+      </c>
+      <c r="E359" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>適切（てきせつ）</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>适当的</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>→ 適切な対応。</t>
+        </is>
+      </c>
+      <c r="D360" s="1" t="n">
+        <v>46084.62761646991</v>
+      </c>
+      <c r="E360" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>自由（じゆう）</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>自由的</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>→ 自由な時間。</t>
+        </is>
+      </c>
+      <c r="D361" s="1" t="n">
+        <v>46084.58076762732</v>
+      </c>
+      <c r="E361" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>ちょうど</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>正好</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>→ ちょうどいい時間。</t>
+        </is>
+      </c>
+      <c r="D362" s="1" t="n">
+        <v>46084.62545873842</v>
+      </c>
+      <c r="E362" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>広がる（ひろがる）</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>扩大（自动）</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>→ 被害が広がった。</t>
+        </is>
+      </c>
+      <c r="D363" s="1" t="n">
+        <v>46084.58098454861</v>
+      </c>
+      <c r="E363" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>曲げる（まげる）</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>弯曲</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>→ 金属を曲げる。</t>
+        </is>
+      </c>
+      <c r="D364" s="1" t="n">
+        <v>46084.69295435185</v>
+      </c>
+      <c r="E364" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>発達する（はったつする）</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>发达</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>→ 技術が発達した。</t>
+        </is>
+      </c>
+      <c r="D365" s="1" t="n">
+        <v>46084.69785101852</v>
+      </c>
+      <c r="E365" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>ところで</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>顺便一提</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>→ ところで、昨日の話は？</t>
+        </is>
+      </c>
+      <c r="D366" s="1" t="n">
+        <v>46084.58174422454</v>
+      </c>
+      <c r="E366" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>滞在（たいざい）</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>停留</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>→ 日本に一年間滞在した。</t>
+        </is>
+      </c>
+      <c r="D367" s="1" t="n">
+        <v>46084.58197560185</v>
+      </c>
+      <c r="E367" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>救助（きゅうじょ）</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>救助</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>→ 救助活動が続いている。</t>
+        </is>
+      </c>
+      <c r="D368" s="1" t="n">
+        <v>46084.71559047454</v>
+      </c>
+      <c r="E368" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>在庫（ざいこ）</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>库存</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>→ 在庫を確認する。</t>
+        </is>
+      </c>
+      <c r="D369" s="1" t="n">
+        <v>46084.70981840278</v>
+      </c>
+      <c r="E369" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>上級者（じょうきゅうしゃ）</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>高级者</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>→ 上級者向けのコースだ。</t>
+        </is>
+      </c>
+      <c r="D370" s="1" t="n">
+        <v>46084.58343795139</v>
+      </c>
+      <c r="E370" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>捕まる（つかまる）</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>被抓住</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>→ 犯人が捕まった。</t>
+        </is>
+      </c>
+      <c r="D371" s="1" t="n">
+        <v>46084.70986123843</v>
+      </c>
+      <c r="E371" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>宿題（しゅくだい）</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>作业</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>→ 宿題を提出する。</t>
+        </is>
+      </c>
+      <c r="D372" s="1" t="n">
+        <v>46084.58385424768</v>
+      </c>
+      <c r="E372" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>渋滞（じゅうたい）</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>堵车</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>→ 道路が渋滞している。</t>
+        </is>
+      </c>
+      <c r="D373" s="1" t="n">
+        <v>46084.71746399305</v>
+      </c>
+      <c r="E373" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>表す（あらわす）</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>表达</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>→ 感謝を表す。</t>
+        </is>
+      </c>
+      <c r="D374" s="1" t="n">
+        <v>46084.71661636574</v>
+      </c>
+      <c r="E374" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>強める（つよめる）</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>→ 対策を強める。</t>
+        </is>
+      </c>
+      <c r="D375" s="1" t="n">
+        <v>46084.59618061343</v>
+      </c>
+      <c r="E375" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>机（つくえ）</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>书桌</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>→ 机の上にパソコンがある。</t>
+        </is>
+      </c>
+      <c r="D376" s="1" t="n">
+        <v>46084.59993554398</v>
+      </c>
+      <c r="E376" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>棚（たな）</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>架子</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>→ 棚に本を並べる。</t>
+        </is>
+      </c>
+      <c r="D377" s="1" t="n">
+        <v>46084.59996734954</v>
+      </c>
+      <c r="E377" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>月曜日（げつようび）</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>星期一</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>→ 月曜日は忙しい。</t>
+        </is>
+      </c>
+      <c r="D378" s="1" t="n">
+        <v>46084.59999623842</v>
+      </c>
+      <c r="E378" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>火曜日（かようび）</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>星期二</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>→ 火曜日に会議がある。</t>
+        </is>
+      </c>
+      <c r="D379" s="1" t="n">
+        <v>46084.72236417824</v>
+      </c>
+      <c r="E379" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>一月（いちがつ）</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>一月</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>→ 一月は寒い。</t>
+        </is>
+      </c>
+      <c r="D380" s="1" t="n">
+        <v>46084.60003518518</v>
+      </c>
+      <c r="E380" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>飛行機（ひこうき）</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>飞机</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>→ 飛行機に乗る。</t>
+        </is>
+      </c>
+      <c r="D381" s="1" t="n">
+        <v>46084.60581012732</v>
+      </c>
+      <c r="E381" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>テーブル</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>桌子</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>→ テーブルを拭く。</t>
+        </is>
+      </c>
+      <c r="D382" s="1" t="n">
+        <v>46084.60603821759</v>
+      </c>
+      <c r="E382" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>猫（ねこ）</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>猫</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>→ 猫が寝ている。</t>
+        </is>
+      </c>
+      <c r="D383" s="1" t="n">
+        <v>46084.60765297454</v>
+      </c>
+      <c r="E383" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>九月（くがつ）</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>九月</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>→ 九月に運動会がある。</t>
+        </is>
+      </c>
+      <c r="D384" s="1" t="n">
+        <v>46084.6078103125</v>
+      </c>
+      <c r="E384" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>口（くち）</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>嘴巴</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>→ 口を開ける。</t>
+        </is>
+      </c>
+      <c r="D385" s="1" t="n">
+        <v>46084.70082736111</v>
+      </c>
+      <c r="E385" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>ご飯（ごはん）</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>米饭</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>→ ご飯をおかわりする。</t>
+        </is>
+      </c>
+      <c r="D386" s="1" t="n">
+        <v>46084.6081675463</v>
+      </c>
+      <c r="E386" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>茶色（ちゃいろ）</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>棕色</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>→ 茶色の机。</t>
+        </is>
+      </c>
+      <c r="D387" s="1" t="n">
+        <v>46084.68553546297</v>
+      </c>
+      <c r="E387" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>父（ちち）</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>父亲</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>→ 父は会社員だ。</t>
+        </is>
+      </c>
+      <c r="D388" s="1" t="n">
+        <v>46084.60908996528</v>
+      </c>
+      <c r="E388" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>寿司（すし）</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>寿司</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>→ 寿司を食べる。</t>
+        </is>
+      </c>
+      <c r="D389" s="1" t="n">
+        <v>46084.62724336806</v>
+      </c>
+      <c r="E389" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>山（やま）</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>山</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>→ 山に登る。</t>
+        </is>
+      </c>
+      <c r="D390" s="1" t="n">
+        <v>46084.71035495371</v>
+      </c>
+      <c r="E390" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>刺身（さしみ）</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>生鱼片</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>→ 刺身は新鮮だ。</t>
+        </is>
+      </c>
+      <c r="D391" s="1" t="n">
+        <v>46084.60939775463</v>
+      </c>
+      <c r="E391" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>水（みず）</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>→ 水が飲みたい。</t>
+        </is>
+      </c>
+      <c r="D392" s="1" t="n">
+        <v>46084.60970892361</v>
+      </c>
+      <c r="E392" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>海（うみ）</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>海</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>→ 海で泳ぐ。</t>
+        </is>
+      </c>
+      <c r="D393" s="1" t="n">
+        <v>46084.60975375</v>
+      </c>
+      <c r="E393" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>足（あし）</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>脚</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>→ 足が速い。</t>
+        </is>
+      </c>
+      <c r="D394" s="1" t="n">
+        <v>46084.60989832176</v>
+      </c>
+      <c r="E394" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>八月（はちがつ）</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>八月</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>→ 八月は暑い。</t>
+        </is>
+      </c>
+      <c r="D395" s="1" t="n">
+        <v>46084.61002613426</v>
+      </c>
+      <c r="E395" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>日曜日（にちようび）</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>→ 日曜日はゆっくり休む。</t>
+        </is>
+      </c>
+      <c r="D396" s="1" t="n">
+        <v>46084.61029207176</v>
+      </c>
+      <c r="E396" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>紫（むらさき）</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>→ 紫の花。</t>
+        </is>
+      </c>
+      <c r="D397" s="1" t="n">
+        <v>46084.71636520833</v>
+      </c>
+      <c r="E397" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>カレーライス</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>咖喱饭</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>→ カレーライスが大好きだ。</t>
+        </is>
+      </c>
+      <c r="D398" s="1" t="n">
+        <v>46084.6104668287</v>
+      </c>
+      <c r="E398" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>エアコン</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>空调</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>→ エアコンをつける。</t>
+        </is>
+      </c>
+      <c r="D399" s="1" t="n">
+        <v>46084.6148796412</v>
+      </c>
+      <c r="E399" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>財布（さいふ）</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>钱包</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>→ 財布を落とした。</t>
+        </is>
+      </c>
+      <c r="D400" s="1" t="n">
+        <v>46084.61532137731</v>
+      </c>
+      <c r="E400" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>中（なか）</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>里面</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>→ 箱の中に何がある？</t>
+        </is>
+      </c>
+      <c r="D401" s="1" t="n">
+        <v>46084.61552140046</v>
+      </c>
+      <c r="E401" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>姉（あね）</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>姐姐</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>→ 姉と買い物に行く。</t>
+        </is>
+      </c>
+      <c r="D402" s="1" t="n">
+        <v>46084.61568517361</v>
+      </c>
+      <c r="E402" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>緑（みどり）</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>→ 緑の葉っぱ。</t>
+        </is>
+      </c>
+      <c r="D403" s="1" t="n">
+        <v>46084.71513230324</v>
+      </c>
+      <c r="E403" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>黒（くろ）</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>→ 黒い猫がいる。</t>
+        </is>
+      </c>
+      <c r="D404" s="1" t="n">
+        <v>46084.62676909722</v>
+      </c>
+      <c r="E404" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>鉛筆（えんぴつ）</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>铅笔</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>→ 鉛筆で書く。</t>
+        </is>
+      </c>
+      <c r="D405" s="1" t="n">
+        <v>46084.6164797338</v>
+      </c>
+      <c r="E405" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>目（め）</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>眼睛</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>→ 目が疲れた。</t>
+        </is>
+      </c>
+      <c r="D406" s="1" t="n">
+        <v>46084.64566180555</v>
+      </c>
+      <c r="E406" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>後ろ（うしろ）</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>后面</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>→ 車の後ろに自転車。</t>
+        </is>
+      </c>
+      <c r="D407" s="1" t="n">
+        <v>46084.6298508912</v>
+      </c>
+      <c r="E407" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>五月（ごがつ）</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>五月</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>→ 五月は気持ちいい。</t>
+        </is>
+      </c>
+      <c r="D408" s="1" t="n">
+        <v>46084.61665422453</v>
+      </c>
+      <c r="E408" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>魚（さかな）</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>鱼</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>→ 魚を釣る。</t>
+        </is>
+      </c>
+      <c r="D409" s="1" t="n">
+        <v>46084.71116013889</v>
+      </c>
+      <c r="E409" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>上（うえ）</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>上面</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>→ 机の上に本がある。</t>
+        </is>
+      </c>
+      <c r="D410" s="1" t="n">
+        <v>46084.62973938658</v>
+      </c>
+      <c r="E410" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>白（しろ）</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>→ 白い雪が積もる。</t>
+        </is>
+      </c>
+      <c r="D411" s="1" t="n">
+        <v>46084.62778224537</v>
+      </c>
+      <c r="E411" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>朝（あさ）</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>早上</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>→ 朝早く起きる。</t>
+        </is>
+      </c>
+      <c r="D412" s="1" t="n">
+        <v>46084.61766839121</v>
+      </c>
+      <c r="E412" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>広がる（ひろがる）</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>扩展</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>→ 被害が広がる。</t>
+        </is>
+      </c>
+      <c r="D413" s="1" t="n">
+        <v>46084.71092206019</v>
+      </c>
+      <c r="E413" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>黄色（きいろ）</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>黄色</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>→ 黄色いバナナ。</t>
+        </is>
+      </c>
+      <c r="D414" s="1" t="n">
+        <v>46084.72103851852</v>
+      </c>
+      <c r="E414" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>顔（かお）</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>脸</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>→ 顔を洗う。</t>
+        </is>
+      </c>
+      <c r="D415" s="1" t="n">
+        <v>46084.72928792824</v>
+      </c>
+      <c r="E415" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>犬（いぬ）</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>狗</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>→ 犬を散歩させる。</t>
+        </is>
+      </c>
+      <c r="D416" s="1" t="n">
+        <v>46084.72929630787</v>
+      </c>
+      <c r="E416" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>毎日（まいにち）</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>每天</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>→ 毎日ジョギングする。</t>
+        </is>
+      </c>
+      <c r="D417" s="1" t="n">
+        <v>46084.72946673611</v>
+      </c>
+      <c r="E417" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>消しゴム（けしごむ）</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>橡皮</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>→ 消しゴムが小さい。</t>
+        </is>
+      </c>
+      <c r="D418" s="1" t="n">
+        <v>46084.7425671875</v>
+      </c>
+      <c r="E418" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>汚い（きたない）</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>脏的</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>→ 汚い部屋。</t>
+        </is>
+      </c>
+      <c r="D419" s="1" t="n">
+        <v>46084.74262543982</v>
+      </c>
+      <c r="E419" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>不便（ふべん）</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>不便的</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>→ この駅は不便だ。</t>
+        </is>
+      </c>
+      <c r="D420" s="1" t="n">
+        <v>46084.74283509259</v>
+      </c>
+      <c r="E420" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>強い（つよい）</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>强的</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>→ 強い風。</t>
+        </is>
+      </c>
+      <c r="D421" s="1" t="n">
+        <v>46084.74284380787</v>
+      </c>
+      <c r="E421" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>二月（にがつ）</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>二月</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>→ 二月に雪が降る。</t>
+        </is>
+      </c>
+      <c r="D422" s="1" t="n">
+        <v>46084.74285145833</v>
+      </c>
+      <c r="E422" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>ますます</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>越来越</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>→ 景気がますます良くなる。</t>
+        </is>
+      </c>
+      <c r="D423" s="1" t="n">
+        <v>46084.74287327546</v>
+      </c>
+      <c r="E423" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>集める（あつめる）</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>收集/聚集（他动）</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>→ 資料を集める。</t>
+        </is>
+      </c>
+      <c r="D424" s="1" t="n">
+        <v>46084.74289827546</v>
+      </c>
+      <c r="E424" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>自転車（じてんしゃ）</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>自行车</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>→ 自転車に乗る。</t>
+        </is>
+      </c>
+      <c r="D425" s="1" t="n">
+        <v>46084.74291005787</v>
+      </c>
+      <c r="E425" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>しかし</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>但是</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>→ 行きたい、しかし忙しい。</t>
+        </is>
+      </c>
+      <c r="D426" s="1" t="n">
+        <v>46084.74292094463</v>
+      </c>
+      <c r="E426" t="n">
         <v>1</v>
       </c>
     </row>

--- a/wrong_words.xlsx
+++ b/wrong_words.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E426"/>
+  <dimension ref="A1:E497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,10 +460,10 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" s="1" t="n">
-        <v>46080.46063228009</v>
+        <v>46085.59571748842</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -650,10 +650,10 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" s="1" t="n">
-        <v>46080.4666321412</v>
+        <v>46085.59546012731</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -954,10 +954,10 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" s="1" t="n">
-        <v>46080.46665704861</v>
+        <v>46085.59568783564</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -973,10 +973,10 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" s="1" t="n">
-        <v>46080.46665885417</v>
+        <v>46085.41369559028</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1163,10 +1163,10 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" s="1" t="n">
-        <v>46084.38787023148</v>
+        <v>46085.56613880787</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -1239,10 +1239,10 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" s="1" t="n">
-        <v>46084.44049435185</v>
+        <v>46085.4586505324</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -1410,10 +1410,10 @@
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" s="1" t="n">
-        <v>46080.4667040162</v>
+        <v>46085.43130745371</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46080.59345513889</v>
+        <v>46085.57158321759</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46084.46704262732</v>
+        <v>46085.55002826389</v>
       </c>
       <c r="E125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46084.48272568287</v>
+        <v>46085.55629259259</v>
       </c>
       <c r="E139" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46084.44076814815</v>
+        <v>46085.46353802083</v>
       </c>
       <c r="E140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46084.4738137963</v>
+        <v>46085.55712922454</v>
       </c>
       <c r="E158" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159">
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46084.46115052083</v>
+        <v>46085.49206568287</v>
       </c>
       <c r="E163" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164">
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46084.3858132176</v>
+        <v>46085.44164283565</v>
       </c>
       <c r="E197" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198">
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>46084.544113125</v>
+        <v>46085.4662382176</v>
       </c>
       <c r="E273" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="274">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>46084.54716353009</v>
+        <v>46085.49490724537</v>
       </c>
       <c r="E284" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285">
@@ -6704,10 +6704,10 @@
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" s="1" t="n">
-        <v>46084.45362160879</v>
+        <v>46085.4611209375</v>
       </c>
       <c r="E286" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="287">
@@ -6926,10 +6926,10 @@
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" s="1" t="n">
-        <v>46084.43450782407</v>
+        <v>46085.44096334491</v>
       </c>
       <c r="E296" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="297">
@@ -6995,10 +6995,10 @@
         </is>
       </c>
       <c r="D299" s="1" t="n">
-        <v>46084.54533444445</v>
+        <v>46085.49053821759</v>
       </c>
       <c r="E299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D307" s="1" t="n">
-        <v>46084.46246259259</v>
+        <v>46085.46478925926</v>
       </c>
       <c r="E307" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="308">
@@ -7202,10 +7202,10 @@
         </is>
       </c>
       <c r="D308" s="1" t="n">
-        <v>46084.47725706019</v>
+        <v>46085.44105104166</v>
       </c>
       <c r="E308" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="309">
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="D309" s="1" t="n">
-        <v>46084.54694444445</v>
+        <v>46085.55747336806</v>
       </c>
       <c r="E309" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="310">
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="D317" s="1" t="n">
-        <v>46084.56998149306</v>
+        <v>46085.56104850694</v>
       </c>
       <c r="E317" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="318">
@@ -7501,10 +7501,10 @@
         </is>
       </c>
       <c r="D321" s="1" t="n">
-        <v>46084.55636740741</v>
+        <v>46085.46330445602</v>
       </c>
       <c r="E321" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="322">
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="D346" s="1" t="n">
-        <v>46084.5768980787</v>
+        <v>46085.55673769676</v>
       </c>
       <c r="E346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="347">
@@ -8095,10 +8095,10 @@
         </is>
       </c>
       <c r="D347" s="1" t="n">
-        <v>46084.57725140046</v>
+        <v>46085.55926263889</v>
       </c>
       <c r="E347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348">
@@ -8164,10 +8164,10 @@
         </is>
       </c>
       <c r="D350" s="1" t="n">
-        <v>46084.62577748843</v>
+        <v>46085.46723412037</v>
       </c>
       <c r="E350" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="351">
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="D352" s="1" t="n">
-        <v>46084.71062622685</v>
+        <v>46085.46186973379</v>
       </c>
       <c r="E352" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="353">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D353" s="1" t="n">
-        <v>46084.70124829861</v>
+        <v>46085.56043258102</v>
       </c>
       <c r="E353" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="354">
@@ -8436,10 +8436,10 @@
         </is>
       </c>
       <c r="D362" s="1" t="n">
-        <v>46084.62545873842</v>
+        <v>46085.49030084491</v>
       </c>
       <c r="E362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="363">
@@ -8528,10 +8528,10 @@
         </is>
       </c>
       <c r="D366" s="1" t="n">
-        <v>46084.58174422454</v>
+        <v>46085.55615290509</v>
       </c>
       <c r="E366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D367" s="1" t="n">
-        <v>46084.58197560185</v>
+        <v>46085.55736751157</v>
       </c>
       <c r="E367" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="368">
@@ -8574,10 +8574,10 @@
         </is>
       </c>
       <c r="D368" s="1" t="n">
-        <v>46084.71559047454</v>
+        <v>46085.44381866898</v>
       </c>
       <c r="E368" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="369">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="D371" s="1" t="n">
-        <v>46084.70986123843</v>
+        <v>46085.55973086806</v>
       </c>
       <c r="E371" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="372">
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="D373" s="1" t="n">
-        <v>46084.71746399305</v>
+        <v>46085.49006585648</v>
       </c>
       <c r="E373" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="374">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D374" s="1" t="n">
-        <v>46084.71661636574</v>
+        <v>46085.55901270833</v>
       </c>
       <c r="E374" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="375">
@@ -9080,10 +9080,10 @@
         </is>
       </c>
       <c r="D390" s="1" t="n">
-        <v>46084.71035495371</v>
+        <v>46085.49361466435</v>
       </c>
       <c r="E390" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="391">
@@ -9172,10 +9172,10 @@
         </is>
       </c>
       <c r="D394" s="1" t="n">
-        <v>46084.60989832176</v>
+        <v>46085.56274613426</v>
       </c>
       <c r="E394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="D397" s="1" t="n">
-        <v>46084.71636520833</v>
+        <v>46085.46119431713</v>
       </c>
       <c r="E397" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="398">
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="D403" s="1" t="n">
-        <v>46084.71513230324</v>
+        <v>46085.4574737037</v>
       </c>
       <c r="E403" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="404">
@@ -9448,10 +9448,10 @@
         </is>
       </c>
       <c r="D406" s="1" t="n">
-        <v>46084.64566180555</v>
+        <v>46085.55964153935</v>
       </c>
       <c r="E406" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="407">
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="D408" s="1" t="n">
-        <v>46084.61665422453</v>
+        <v>46085.56791520833</v>
       </c>
       <c r="E408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="D410" s="1" t="n">
-        <v>46084.62973938658</v>
+        <v>46085.55845943287</v>
       </c>
       <c r="E410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -9609,10 +9609,10 @@
         </is>
       </c>
       <c r="D413" s="1" t="n">
-        <v>46084.71092206019</v>
+        <v>46085.49896224537</v>
       </c>
       <c r="E413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="D418" s="1" t="n">
-        <v>46084.7425671875</v>
+        <v>46085.42090753472</v>
       </c>
       <c r="E418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -9908,10 +9908,1639 @@
         </is>
       </c>
       <c r="D426" s="1" t="n">
-        <v>46084.74292094463</v>
+        <v>46084.74292094907</v>
       </c>
       <c r="E426" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>説明（せつめい）</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>→ 理由を説明してください。</t>
+        </is>
+      </c>
+      <c r="D427" s="1" t="n">
+        <v>46085.56919793982</v>
+      </c>
+      <c r="E427" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>延期（えんき）</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>延期</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>→ 会議が延期された。</t>
+        </is>
+      </c>
+      <c r="D428" s="1" t="n">
+        <v>46085.56447107639</v>
+      </c>
+      <c r="E428" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>選挙（せんきょ）</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>选举</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>→ 国会議員の選挙がある。</t>
+        </is>
+      </c>
+      <c r="D429" s="1" t="n">
+        <v>46085.57136212963</v>
+      </c>
+      <c r="E429" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>多い（おおい）</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>多的</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>→ 人が多い。</t>
+        </is>
+      </c>
+      <c r="D430" s="1" t="n">
+        <v>46085.41377336805</v>
+      </c>
+      <c r="E430" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>確認する（かくにんする）</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>确认</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>→ 内容を確認する。</t>
+        </is>
+      </c>
+      <c r="D431" s="1" t="n">
+        <v>46085.41398450232</v>
+      </c>
+      <c r="E431" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>ほぼ</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>几乎</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>→ ほぼ完成した。</t>
+        </is>
+      </c>
+      <c r="D432" s="1" t="n">
+        <v>46085.41409586806</v>
+      </c>
+      <c r="E432" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>隠れる（かくれる）</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>隐藏（自动）</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>→ 猫が隠れている。</t>
+        </is>
+      </c>
+      <c r="D433" s="1" t="n">
+        <v>46085.57847840278</v>
+      </c>
+      <c r="E433" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>昨日（きのう）</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>昨天</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>→ 昨日は雨だった。</t>
+        </is>
+      </c>
+      <c r="D434" s="1" t="n">
+        <v>46085.56855459491</v>
+      </c>
+      <c r="E434" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>進化する（しんかする）</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>进化</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>→ 技術が進化する。</t>
+        </is>
+      </c>
+      <c r="D435" s="1" t="n">
+        <v>46085.56543638889</v>
+      </c>
+      <c r="E435" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>冷たい（つめたい）</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>冷的（物体）</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>→ 冷たい水。</t>
+        </is>
+      </c>
+      <c r="D436" s="1" t="n">
+        <v>46085.56834962963</v>
+      </c>
+      <c r="E436" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>応募（おうぼ）</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>应聘</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>→ その会社に応募した。</t>
+        </is>
+      </c>
+      <c r="D437" s="1" t="n">
+        <v>46085.41583615741</v>
+      </c>
+      <c r="E437" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>さらに</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>更进一步/而且</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>→ 勉強し、さらに運動もする。</t>
+        </is>
+      </c>
+      <c r="D438" s="1" t="n">
+        <v>46085.41657555556</v>
+      </c>
+      <c r="E438" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>感じる（かんじる）</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>感觉</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>→ 幸せを感じる。</t>
+        </is>
+      </c>
+      <c r="D439" s="1" t="n">
+        <v>46085.4169058449</v>
+      </c>
+      <c r="E439" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>避難（ひなん）</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>避难</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>→ 住民が避難した。</t>
+        </is>
+      </c>
+      <c r="D440" s="1" t="n">
+        <v>46085.56724761574</v>
+      </c>
+      <c r="E440" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>汚い（きたない）</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>脏</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>→ 汚い手。</t>
+        </is>
+      </c>
+      <c r="D441" s="1" t="n">
+        <v>46085.57682268519</v>
+      </c>
+      <c r="E441" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>じつは（実は）</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>其实</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>→ 実は秘密だ。</t>
+        </is>
+      </c>
+      <c r="D442" s="1" t="n">
+        <v>46085.56232923611</v>
+      </c>
+      <c r="E442" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>質問（しつもん）</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>提问</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>→ 質問があります。</t>
+        </is>
+      </c>
+      <c r="D443" s="1" t="n">
+        <v>46085.42504681713</v>
+      </c>
+      <c r="E443" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>危険（きけん）</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>危险的</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>→ 危険な道。</t>
+        </is>
+      </c>
+      <c r="D444" s="1" t="n">
+        <v>46085.56904516204</v>
+      </c>
+      <c r="E444" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>悩む（なやむ）</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>烦恼</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>→ 将来のことで悩む。</t>
+        </is>
+      </c>
+      <c r="D445" s="1" t="n">
+        <v>46085.42585115741</v>
+      </c>
+      <c r="E445" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>有利（ゆうり）</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>有利的</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>→ 有利な条件。</t>
+        </is>
+      </c>
+      <c r="D446" s="1" t="n">
+        <v>46085.42601325231</v>
+      </c>
+      <c r="E446" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>温度（おんど）</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>温度</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>→ 室内の温度を下げる。</t>
+        </is>
+      </c>
+      <c r="D447" s="1" t="n">
+        <v>46085.42804033565</v>
+      </c>
+      <c r="E447" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>気をつける（きをつける）</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>小心</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>→ 道路で気をつける。</t>
+        </is>
+      </c>
+      <c r="D448" s="1" t="n">
+        <v>46085.57207383102</v>
+      </c>
+      <c r="E448" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>学ぶ（まなぶ）</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>→ 大学で経済学を学ぶ。</t>
+        </is>
+      </c>
+      <c r="D449" s="1" t="n">
+        <v>46085.57565561343</v>
+      </c>
+      <c r="E449" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>禁止（きんし）</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>→ ここでの喫煙は禁止されている。</t>
+        </is>
+      </c>
+      <c r="D450" s="1" t="n">
+        <v>46085.57202824074</v>
+      </c>
+      <c r="E450" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>年金（ねんきん）</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>养老金</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>→ 年金を受け取る。</t>
+        </is>
+      </c>
+      <c r="D451" s="1" t="n">
+        <v>46085.42965166667</v>
+      </c>
+      <c r="E451" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>症状（しょうじょう）</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>症状</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>→ 症状が悪化している。</t>
+        </is>
+      </c>
+      <c r="D452" s="1" t="n">
+        <v>46085.42969511574</v>
+      </c>
+      <c r="E452" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>滞留（たいりゅう）</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>滞留</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>→ 空港で滞留している。</t>
+        </is>
+      </c>
+      <c r="D453" s="1" t="n">
+        <v>46085.57333302083</v>
+      </c>
+      <c r="E453" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>増やす（ふやす）</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>增加（他动）</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>→ 売上を増やす。</t>
+        </is>
+      </c>
+      <c r="D454" s="1" t="n">
+        <v>46085.57827207176</v>
+      </c>
+      <c r="E454" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>深まる（ふかまる）</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>加深</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>→ 理解が深まる。</t>
+        </is>
+      </c>
+      <c r="D455" s="1" t="n">
+        <v>46085.5753853588</v>
+      </c>
+      <c r="E455" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>大事（だいじ）</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>重要的</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>→ 大事な書類。</t>
+        </is>
+      </c>
+      <c r="D456" s="1" t="n">
+        <v>46085.57489517361</v>
+      </c>
+      <c r="E456" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>消す（けす）</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>关闭/消除</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>→ 電気を消す。</t>
+        </is>
+      </c>
+      <c r="D457" s="1" t="n">
+        <v>46085.43107415509</v>
+      </c>
+      <c r="E457" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>それにしても</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>话虽如此</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>→ それにしても暑い日だ。</t>
+        </is>
+      </c>
+      <c r="D458" s="1" t="n">
+        <v>46085.43153092593</v>
+      </c>
+      <c r="E458" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>不完全（ふかんぜん）</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>不完全的</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>→ 不完全な作品。</t>
+        </is>
+      </c>
+      <c r="D459" s="1" t="n">
+        <v>46085.57048712963</v>
+      </c>
+      <c r="E459" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>なおかつ</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>并且/而且</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>→ 安くて、なおかつ便利だ。</t>
+        </is>
+      </c>
+      <c r="D460" s="1" t="n">
+        <v>46085.57342327546</v>
+      </c>
+      <c r="E460" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>四月（しがつ）</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>四月</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>→ 四月に桜が咲く。</t>
+        </is>
+      </c>
+      <c r="D461" s="1" t="n">
+        <v>46085.57940520834</v>
+      </c>
+      <c r="E461" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>暖まる（あたたまる）</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>变暖</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>→ 部屋が暖まる。</t>
+        </is>
+      </c>
+      <c r="D462" s="1" t="n">
+        <v>46085.58363177083</v>
+      </c>
+      <c r="E462" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>交通（こうつう）</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>→ 交通が便利だ。</t>
+        </is>
+      </c>
+      <c r="D463" s="1" t="n">
+        <v>46085.60695621528</v>
+      </c>
+      <c r="E463" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>届け出（とどけで）</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>申报</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>→ 住所変更の届け出を出す。</t>
+        </is>
+      </c>
+      <c r="D464" s="1" t="n">
+        <v>46085.61597322916</v>
+      </c>
+      <c r="E464" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>輸送（ゆそう）</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>运输</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>→ 商品を輸送する。</t>
+        </is>
+      </c>
+      <c r="D465" s="1" t="n">
+        <v>46085.61631877315</v>
+      </c>
+      <c r="E465" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>高める（たかめる）</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>提高</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>→ 技術を高める。</t>
+        </is>
+      </c>
+      <c r="D466" s="1" t="n">
+        <v>46085.58840946759</v>
+      </c>
+      <c r="E466" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>体験（たいけん）</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>→ 日本文化を体験する。</t>
+        </is>
+      </c>
+      <c r="D467" s="1" t="n">
+        <v>46085.58859509259</v>
+      </c>
+      <c r="E467" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>無名（むめい）</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>无名的</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>→ 無名の歌手。</t>
+        </is>
+      </c>
+      <c r="D468" s="1" t="n">
+        <v>46085.58875997685</v>
+      </c>
+      <c r="E468" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>特別（とくべつ）</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>特别的</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>→ 特別な日。</t>
+        </is>
+      </c>
+      <c r="D469" s="1" t="n">
+        <v>46085.58882372685</v>
+      </c>
+      <c r="E469" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>運賃（うんちん）</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>车费</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>→ 運賃を払う。</t>
+        </is>
+      </c>
+      <c r="D470" s="1" t="n">
+        <v>46085.61382116898</v>
+      </c>
+      <c r="E470" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>育成（いくせい）</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>培养</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>→ 人材育成に力を入れる。</t>
+        </is>
+      </c>
+      <c r="D471" s="1" t="n">
+        <v>46085.60734462963</v>
+      </c>
+      <c r="E471" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>裁判（さいばん）</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>审判</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>→ 裁判が始まった。</t>
+        </is>
+      </c>
+      <c r="D472" s="1" t="n">
+        <v>46085.60928553241</v>
+      </c>
+      <c r="E472" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>耳（みみ）</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>耳朵</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>→ 耳がいい。</t>
+        </is>
+      </c>
+      <c r="D473" s="1" t="n">
+        <v>46085.58943248843</v>
+      </c>
+      <c r="E473" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>多数（たすう）</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>多数</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>→ 多数の人が集まった。</t>
+        </is>
+      </c>
+      <c r="D474" s="1" t="n">
+        <v>46085.61328388889</v>
+      </c>
+      <c r="E474" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>続く（つづく）</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>持续</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>→ 雨が一週間続いた。</t>
+        </is>
+      </c>
+      <c r="D475" s="1" t="n">
+        <v>46085.5898440625</v>
+      </c>
+      <c r="E475" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>監督する（かんとくする）</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>监督</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>→ 工事を監督する。</t>
+        </is>
+      </c>
+      <c r="D476" s="1" t="n">
+        <v>46085.61385740741</v>
+      </c>
+      <c r="E476" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>祖母（そぼ）</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>祖母</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>→ 祖母に手紙を書く。</t>
+        </is>
+      </c>
+      <c r="D477" s="1" t="n">
+        <v>46085.60768875</v>
+      </c>
+      <c r="E477" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>軽い（かるい）</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>轻的</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>→ 荷物が軽い。</t>
+        </is>
+      </c>
+      <c r="D478" s="1" t="n">
+        <v>46085.61372658565</v>
+      </c>
+      <c r="E478" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>残る（のこる）</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>剩下</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>→ 食べ物が残った。</t>
+        </is>
+      </c>
+      <c r="D479" s="1" t="n">
+        <v>46085.61510195602</v>
+      </c>
+      <c r="E479" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>練習する（れんしゅうする）</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>练习</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>→ 毎日練習する。</t>
+        </is>
+      </c>
+      <c r="D480" s="1" t="n">
+        <v>46085.59524332176</v>
+      </c>
+      <c r="E480" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>通す（とおす）</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>让…通过</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>→ 書類を通す。</t>
+        </is>
+      </c>
+      <c r="D481" s="1" t="n">
+        <v>46085.59527533565</v>
+      </c>
+      <c r="E481" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>速度（そくど）</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>速度</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>→ 車の速度を上げる。</t>
+        </is>
+      </c>
+      <c r="D482" s="1" t="n">
+        <v>46085.60416527778</v>
+      </c>
+      <c r="E482" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>崩す（くずす）</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>弄坏/拆散</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>→ 壁を崩す。</t>
+        </is>
+      </c>
+      <c r="D483" s="1" t="n">
+        <v>46085.61827869213</v>
+      </c>
+      <c r="E483" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>個人（こじん）</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>个人</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>→ 個人情報を守る。</t>
+        </is>
+      </c>
+      <c r="D484" s="1" t="n">
+        <v>46085.59540482639</v>
+      </c>
+      <c r="E484" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>診断（しんだん）</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>诊断</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>→ 医者が病気を診断した。</t>
+        </is>
+      </c>
+      <c r="D485" s="1" t="n">
+        <v>46085.59542871528</v>
+      </c>
+      <c r="E485" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>乗せる（のせる）</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>让…乘</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>→ 車に友達を乗せる。</t>
+        </is>
+      </c>
+      <c r="D486" s="1" t="n">
+        <v>46085.59548230324</v>
+      </c>
+      <c r="E486" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>賛成（さんせい）</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>赞成</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>→ 私はその意見に賛成だ。</t>
+        </is>
+      </c>
+      <c r="D487" s="1" t="n">
+        <v>46085.61144846065</v>
+      </c>
+      <c r="E487" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>散る（ちる）</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>散落</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>→ 桜の花が散る。</t>
+        </is>
+      </c>
+      <c r="D488" s="1" t="n">
+        <v>46085.61841342778</v>
+      </c>
+      <c r="E488" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>評価する（ひょうかする）</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>评价</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>→ 成績を評価する。</t>
+        </is>
+      </c>
+      <c r="D489" s="1" t="n">
+        <v>46085.60759</v>
+      </c>
+      <c r="E489" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>確実（かくじつ）</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>确实的（※な形容词）</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
+      <c r="D490" s="1" t="n">
+        <v>46085.59562100694</v>
+      </c>
+      <c r="E490" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>貴重（きちょう）</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>珍贵的</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>→ 貴重な経験。</t>
+        </is>
+      </c>
+      <c r="D491" s="1" t="n">
+        <v>46085.61130157408</v>
+      </c>
+      <c r="E491" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>降ろす（おろす）</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>让…下车</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>→ 荷物を降ろす。</t>
+        </is>
+      </c>
+      <c r="D492" s="1" t="n">
+        <v>46085.61408295139</v>
+      </c>
+      <c r="E492" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>予定（よてい）</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>预定</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>→ 明日は予定がある。</t>
+        </is>
+      </c>
+      <c r="D493" s="1" t="n">
+        <v>46085.59569913195</v>
+      </c>
+      <c r="E493" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>嬉しい（うれしい）</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>高兴的</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>→ 試験に合格して嬉しい。</t>
+        </is>
+      </c>
+      <c r="D494" s="1" t="n">
+        <v>46085.59572700231</v>
+      </c>
+      <c r="E494" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>複雑（ふくざつ）</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>复杂的</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>→ 複雑な手続き。</t>
+        </is>
+      </c>
+      <c r="D495" s="1" t="n">
+        <v>46085.59573751158</v>
+      </c>
+      <c r="E495" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>奪う（うばう）</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>夺取</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>→ 財産を奪う。</t>
+        </is>
+      </c>
+      <c r="D496" s="1" t="n">
+        <v>46085.61637196759</v>
+      </c>
+      <c r="E496" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>課程（かてい）</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>课程过程</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>→ この課程は2年間だ。</t>
+        </is>
+      </c>
+      <c r="D497" s="1" t="n">
+        <v>46085.6136600463</v>
+      </c>
+      <c r="E497" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
